--- a/docs/qa/Mill-Smart-Log-Hasil-Uji-Alur.xlsx
+++ b/docs/qa/Mill-Smart-Log-Hasil-Uji-Alur.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B38" s="44" t="inlineStr">
         <is>
-          <t>254 dari 258 jalan yang dapat dijalankan sudah dijalankan: 241 Lulus, 13 Gagal. 4 jalan bertanda "Tidak diuji" — belum diperiksa, BUKAN gagal dan BUKAN lulus. 7 jalan bertanda "Tidak berlaku" dan tidak dihitung sebagai pekerjaan: kasusnya tidak punya apa pun untuk diuji pada varian itu.</t>
+          <t>254 dari 258 jalan yang dapat dijalankan sudah dijalankan: 254 Lulus, 0 Gagal. 4 jalan bertanda "Tidak diuji" — belum diperiksa, BUKAN gagal dan BUKAN lulus. 7 jalan bertanda "Tidak berlaku" dan tidak dihitung sebagai pekerjaan: kasusnya tidak punya apa pun untuk diuji pada varian itu.</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>254 dari 258 jalan yang dapat dijalankan sudah dijalankan dan hasilnya terisi (241 Lulus, 13 Gagal). 4 jalan masih menunggu penguji — kolom Catatan tiap baris menyebut apa yang menghalanginya. 7 jalan bertanda "Tidak berlaku": kasusnya memang tidak punya apa pun untuk diuji pada varian itu. Total baris 265.</t>
+          <t>254 dari 258 jalan yang dapat dijalankan sudah dijalankan dan hasilnya terisi (254 Lulus, 0 Gagal). 4 jalan masih menunggu penguji — kolom Catatan tiap baris menyebut apa yang menghalanginya. 7 jalan bertanda "Tidak berlaku": kasusnya memang tidak punya apa pun untuk diuji pada varian itu. Total baris 265.</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       <c r="Q7" s="17" t="n"/>
       <c r="R7" s="17" t="inlineStr">
         <is>
-          <t>Supervisor Mill A melihat 0 id Production Line dan 20 baris; Supervisor Mill B melihat 0 id dan 4 baris. Id yang muncul di kedua sesi: 0. Nama estate khas Mill B terbaca di sesi Mill A: false. Catatan: pemeriksaan memakai id Production Line, bukan namanya, karena kedua mill sama-sama menamai line pertamanya "Line 1" sehingga nama tidak dapat membedakan keduanya.</t>
+          <t>Supervisor Mill A melihat 0 id Production Line dan 20 baris; Supervisor Mill B melihat 0 id dan 5 baris. Id yang muncul di kedua sesi: 0. Nama estate khas Mill B terbaca di sesi Mill A: false. Catatan: pemeriksaan memakai id Production Line, bukan namanya, karena kedua mill sama-sama menamai line pertamanya "Line 1" sehingga nama tidak dapat membedakan keduanya.</t>
         </is>
       </c>
     </row>
@@ -1647,15 +1647,15 @@
           <t>Pelaksana QA otomatis</t>
         </is>
       </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="P8" s="45" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="Q8" s="17" t="n"/>
       <c r="R8" s="17" t="inlineStr">
         <is>
-          <t>Login ditolak dan tetap di layar Login=true | pesannya: "Business area yang dipilih tidak sesuai dengan akses Anda." | menyebut mill=false | mengarahkan tindakan (hubungi Admin)=false | menyebut pilihan yang tidak pernah dibuat pengguna=true (harus false) | menyuruh memeriksa koneksi=false (harus false)</t>
+          <t>Login ditolak dan tetap di layar Login=true | pesannya: "Akun ini belum terikat pada mill mana pun, sehingga tidak ada data yang dapat dibuka. Hubungi Admin untuk menetapkan mill akun Anda." | menyebut mill=true | mengarahkan tindakan (hubungi Admin)=true | menyebut pilihan yang tidak pernah dibuat pengguna=false (harus false) | menyuruh memeriksa koneksi=false (harus false)</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       <c r="Q15" s="17" t="n"/>
       <c r="R15" s="17" t="inlineStr">
         <is>
-          <t>Laporan Kernel Plant (line="Line 1", periode="QA Masa Depan · 01–28 Feb 2027 · Terbuka"). CSV "laporan-kernel-plant_qa-masa-depan_20261012_023556.csv" 289 bita; nama menyebut stasiun=true; baris pertama adalah judul kolom terbaca=true ("Periode,Mill,"Production Line",Tanggal,"Unit Kernel Plant",Status,Catatan,"Slot Waktu","Ri"); tanpa karakter rusak=true | Excel "laporan-kernel-plant_qa-masa-depan_20261012_023556.xlsx" 2335 bita; arsip xlsx sah=true; memuat [Content_Types].xml=true; memuat xl/workbook.xml=true; nama menyebut stasiun=true. Catatan: keutuhan berkas Excel diperiksa secara struktural (arsip xlsx sah beserta dua entri wajibnya), bukan dengan membukanya di Excel.</t>
+          <t>Laporan Kernel Plant (line="Line 1", periode="QA Masa Depan · 01–28 Feb 2027 · Terbuka"). CSV "laporan-kernel-plant_qa-masa-depan_20261012_064221.csv" 289 bita; nama menyebut stasiun=true; baris pertama adalah judul kolom terbaca=true ("Periode,Mill,"Production Line",Tanggal,"Unit Kernel Plant",Status,Catatan,"Slot Waktu","Ri"); tanpa karakter rusak=true | Excel "laporan-kernel-plant_qa-masa-depan_20261012_064221.xlsx" 2335 bita; arsip xlsx sah=true; memuat [Content_Types].xml=true; memuat xl/workbook.xml=true; nama menyebut stasiun=true. Catatan: keutuhan berkas Excel diperiksa secara struktural (arsip xlsx sah beserta dua entri wajibnya), bukan dengan membukanya di Excel.</t>
         </is>
       </c>
     </row>
@@ -3378,15 +3378,15 @@
           <t>Pelaksana QA otomatis</t>
         </is>
       </c>
-      <c r="P28" s="8" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="P28" s="45" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="Q28" s="17" t="n"/>
       <c r="R28" s="17" t="inlineStr">
         <is>
-          <t>permintaan ditolak=true; pesan galat berada di sebelah kolom password lama (bukan pesan umum di atas form)=false; password tidak berubah — login dengan password lama masih berhasil=true.</t>
+          <t>permintaan ditolak=true; pesan galat berada di sebelah kolom password lama (bukan pesan umum di atas form)=true; password tidak berubah — login dengan password lama masih berhasil=true.</t>
         </is>
       </c>
     </row>
@@ -3548,15 +3548,15 @@
           <t>Pelaksana QA otomatis</t>
         </is>
       </c>
-      <c r="P30" s="8" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="P30" s="45" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="Q30" s="17" t="n"/>
       <c r="R30" s="17" t="inlineStr">
         <is>
-          <t>nama pengguna tercetak=true; ada jalan menuju daftar stasiun yang terlihat=true — kartunya bernama "Production Process Activity", bukan "Station List" (3 kartu menu: Estimates &amp; Baselines, Production Process Activity, Dashboard &amp; Reporting); nama mill lain terlihat=false (harus false); galat teknis=false. NAMA MILL TIDAK TERCETAK di layar ini=true: baris merek berbunyi "Mills Smart Log" — teks tetap, bukan nama mill maupun Nama Aplikasi yang diatur di Mills Setting. Operator tidak punya satu pun penanda mill yang sedang ia isi. Satu akar dengan AD-10.</t>
+          <t>nama pengguna tercetak=true; ada jalan menuju daftar stasiun yang terlihat=true — kartunya bernama "Production Process Activity", bukan "Station List" (3 kartu menu: Estimates &amp; Baselines, Production Process Activity, Dashboard &amp; Reporting); nama mill lain terlihat=false (harus false); galat teknis=false. NAMA MILL TIDAK TERCETAK di layar ini=false: baris merek berbunyi "Business Unit A — Mill Smart Log QA635537" — teks tetap, bukan nama mill maupun Nama Aplikasi yang diatur di Mills Setting. Operator tidak punya satu pun penanda mill yang sedang ia isi. Satu akar dengan AD-10.</t>
         </is>
       </c>
     </row>
@@ -3722,15 +3722,15 @@
           <t>Pelaksana QA otomatis</t>
         </is>
       </c>
-      <c r="P32" s="8" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="P32" s="45" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="Q32" s="17" t="n"/>
       <c r="R32" s="17" t="inlineStr">
         <is>
-          <t>"Line 1" dipilih di Station List: Monitor stasiun menuliskan line itu=false — layar Monitor TIDAK menyebut Production Line sama sekali, bukan menyebut line yang salah; kembali ke Station List pemilihnya masih "Line 1"=true; sesudah aplikasi dibuka ulang dan login ulang pemilihnya masih "Line 1"=true (pilihannya diingat perangkat); sesudah diganti ke "Line 2", Monitor stasiun yang sama kini menuliskan line itu=false.</t>
+          <t>"Line 1" dipilih di Station List: Monitor stasiun menuliskan line itu=true; kembali ke Station List pemilihnya masih "Line 1"=true; sesudah aplikasi dibuka ulang dan login ulang pemilihnya masih "Line 1"=true (pilihannya diingat perangkat); sesudah diganti ke "Line 2", Monitor stasiun yang sama kini menuliskan line itu=true.</t>
         </is>
       </c>
     </row>
@@ -3806,15 +3806,15 @@
           <t>Pelaksana QA otomatis</t>
         </is>
       </c>
-      <c r="P33" s="8" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="P33" s="45" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="Q33" s="17" t="n"/>
       <c r="R33" s="17" t="inlineStr">
         <is>
-          <t>masuk sebagai "operator-noline" (mill "QA Mill Tanpa Line", 0 Production Line): Station List memuat arahan yang menyebut Production Line=false; pilihan line yang ditawarkan=0 (harus 0); tile stasiun=18; layar kosong tanpa keterangan=false (harus false); galat teknis=false (harus false). Isi layar: "Mills Smart Log Home / Production Process Activity Daftar Stasiun Stasiun Aktif Weighbridge Pressing Storage Tank Grading Clarification Effluent Plant Cages Track Engine Room CPO Dispatch Sterilizer Boiler Room Kernel Di"</t>
+          <t>masuk sebagai "operator-noline" (mill "QA Mill Tanpa Line", 0 Production Line): Station List memuat arahan yang menyebut Production Line=true; pilihan line yang ditawarkan=0 (harus 0); tile stasiun=0; layar kosong tanpa keterangan=false (harus false); galat teknis=false (harus false). Isi layar: "Mills Smart Log Home / Production Process Activity Daftar Stasiun Mill ini belum memiliki Production Line Daftar stasiun mengikuti Production Line, jadi belum ada stasiun yang dapat diisi di sini. Silakan hubungi Admin u"</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       <c r="Q36" s="17" t="n"/>
       <c r="R36" s="17" t="inlineStr">
         <is>
-          <t>New Data membuka layar Form=true (/stations/depricarping/form/7eab83f0-d869-48bc-bcbb-1cc1564df3f4); kolom Tanggal terisi otomatis="12 Oktober 2026" dan tidak dapat diubah=true; kolom identitas unit kosong dan dapat diketik=true; grid slot waktu masih kosong — 0 baris.</t>
+          <t>New Data membuka layar Form=true (/stations/depricarping/form/f519c65e-69f9-4f0c-ad75-74e06d9f47ff); kolom Tanggal terisi otomatis="12 Oktober 2026" dan tidak dapat diubah=true; kolom identitas unit kosong dan dapat diketik=true; grid slot waktu masih kosong — 0 baris.</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
       <c r="Q41" s="17" t="n"/>
       <c r="R41" s="17" t="inlineStr">
         <is>
-          <t>Form baru diisi — identitas "QA1098390", 0 baris slot, 9 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA1098390 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
+          <t>Form baru diisi — identitas "QA8900770", 0 baris slot, 9 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA8900770 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       <c r="Q42" s="17" t="n"/>
       <c r="R42" s="17" t="inlineStr">
         <is>
-          <t>satu record Weighbridge "QA1243540" dibuat lebih dulu di perangkat yang sama, karena daftar WB Card No Grading dibaca dari record Weighbridge lokal. Form baru diisi — identitas "QA1344150", 1 baris slot, 11 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA1344150 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
+          <t>satu record Weighbridge "QA9043950" dibuat lebih dulu di perangkat yang sama, karena daftar WB Card No Grading dibaca dari record Weighbridge lokal. Form baru diisi — identitas "QA9144070", 1 baris slot, 11 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA9144070 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       <c r="Q43" s="17" t="n"/>
       <c r="R43" s="17" t="inlineStr">
         <is>
-          <t>Form baru diisi — identitas "QA1516380", 1 baris slot ("00:00"), 4 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA1516380 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
+          <t>Form baru diisi — identitas "QA9315790", 1 baris slot ("00:00"), 4 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA9315790 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4771,7 @@
       <c r="Q44" s="17" t="n"/>
       <c r="R44" s="17" t="inlineStr">
         <is>
-          <t>Form baru diisi — identitas "QA1678480", 1 baris slot, 14 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA1678480 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
+          <t>Form baru diisi — identitas "QA9477110", 1 baris slot, 14 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA9477110 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       <c r="Q45" s="17" t="n"/>
       <c r="R45" s="17" t="inlineStr">
         <is>
-          <t>Form baru diisi — identitas "QA1836830", 1 baris slot ("07:00"), 8 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA1836830 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
+          <t>Form baru diisi — identitas "QA9633410", 1 baris slot ("07:00"), 8 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA9633410 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       <c r="Q46" s="17" t="n"/>
       <c r="R46" s="17" t="inlineStr">
         <is>
-          <t>Form baru diisi — identitas "QA2005000", 1 baris slot ("07:00"), 8 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA2005000 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
+          <t>Form baru diisi — identitas "QA9801050", 1 baris slot ("07:00"), 8 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA9801050 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5038,7 @@
       <c r="Q47" s="17" t="n"/>
       <c r="R47" s="17" t="inlineStr">
         <is>
-          <t>Form baru diisi — identitas "QA2172510", 1 baris slot ("07:00"), 9 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA2172510 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
+          <t>Form baru diisi — identitas "QA9968940", 1 baris slot ("07:00"), 9 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA9968940 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
         </is>
       </c>
     </row>
@@ -5127,7 +5127,7 @@
       <c r="Q48" s="17" t="n"/>
       <c r="R48" s="17" t="inlineStr">
         <is>
-          <t>Form baru diisi — identitas "QA2340980", 1 baris slot ("07:00"), 11 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA2340980 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
+          <t>Form baru diisi — identitas "QA0136860", 1 baris slot ("07:00"), 11 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA0136860 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5216,7 @@
       <c r="Q49" s="17" t="n"/>
       <c r="R49" s="17" t="inlineStr">
         <is>
-          <t>Form baru diisi — identitas "QA2510860", 1 baris slot ("07:00"), 17 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA2510860 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
+          <t>Form baru diisi — identitas "QA0305680", 1 baris slot ("07:00"), 17 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA0305680 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       <c r="Q50" s="17" t="n"/>
       <c r="R50" s="17" t="inlineStr">
         <is>
-          <t>Form baru diisi — identitas "QA2683160", 1 baris slot ("07:00"), 21 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA2683160 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
+          <t>Form baru diisi — identitas "QA0477550", 1 baris slot ("07:00"), 21 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA0477550 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       <c r="Q51" s="17" t="n"/>
       <c r="R51" s="17" t="inlineStr">
         <is>
-          <t>Form baru diisi — identitas "QA2858670", 1 baris slot ("07:00"), 11 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA2858670 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
+          <t>Form baru diisi — identitas "QA0652530", 1 baris slot ("07:00"), 11 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA0652530 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       <c r="Q52" s="17" t="n"/>
       <c r="R52" s="17" t="inlineStr">
         <is>
-          <t>Form baru diisi — identitas "QA3028500", 1 baris slot ("07:00"), 29 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA3028500 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
+          <t>Form baru diisi — identitas "QA0822390", 1 baris slot ("07:00"), 29 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA0822390 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       <c r="Q53" s="17" t="n"/>
       <c r="R53" s="17" t="inlineStr">
         <is>
-          <t>Form baru diisi — identitas "QA3209230", 1 baris slot ("07:00"), 15 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA3209230 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
+          <t>Form baru diisi — identitas "QA1003510", 1 baris slot ("07:00"), 15 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA1003510 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       <c r="Q54" s="17" t="n"/>
       <c r="R54" s="17" t="inlineStr">
         <is>
-          <t>Form baru diisi — identitas "QA4033050", 1 baris slot ("07:00"), 19 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA4033050 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
+          <t>Form baru diisi — identitas "QA1832310", 1 baris slot ("07:00"), 19 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA1832310 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       <c r="Q55" s="17" t="n"/>
       <c r="R55" s="17" t="inlineStr">
         <is>
-          <t>Form baru diisi — identitas "QA3380250", 1 baris slot, 18 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA3380250 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
+          <t>Form baru diisi — identitas "QA1175660", 1 baris slot, 18 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA1175660 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       <c r="Q56" s="17" t="n"/>
       <c r="R56" s="17" t="inlineStr">
         <is>
-          <t>Form baru diisi — identitas "QA3538900", 1 baris slot, 21 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA3538900 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
+          <t>Form baru diisi — identitas "QA1335500", 1 baris slot, 21 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA1335500 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5928,7 @@
       <c r="Q57" s="17" t="n"/>
       <c r="R57" s="17" t="inlineStr">
         <is>
-          <t>Form baru diisi — identitas "QA3699400", 1 baris slot, 22 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA3699400 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
+          <t>Form baru diisi — identitas "QA1496340", 1 baris slot, 22 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA1496340 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6017,7 @@
       <c r="Q58" s="17" t="n"/>
       <c r="R58" s="17" t="inlineStr">
         <is>
-          <t>Form baru diisi — identitas "QA3860180", 1 baris slot ("07:00"), 18 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA3860180 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
+          <t>Form baru diisi — identitas "QA1658460", 1 baris slot ("07:00"), 18 kolom terisi — lalu Simpan: galat validasi=0; layar keluar dari Form=true; pesan konfirmasi terbaca=true; record ditemukan di Data Preview=true dengan status Tersimpan=true ("QA1658460 Tersimpan"). Satu baris terisi sudah cukup — tidak dipaksa mengisi 24 slot.</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       <c r="Q62" s="17" t="n"/>
       <c r="R62" s="17" t="inlineStr">
         <is>
-          <t>identitas "QA8892660" diisi dan satu baris slot "07:00" ditambahkan TANPA satu kolom bacaan pun. Ditolak=true; record tidak tersimpan — layar masih di Form=true; pesannya tercetak di bagian grid, bukan hanya di atas form=true ("Minimal 1 baris Depricarping Detail (Time-Slot terpilih + minimal 1 kolom bacaan terisi) harus diisi sebelum menyimpan."); pesannya menyebut syarat slot DAN minimal satu kolom bacaan=true.</t>
+          <t>identitas "QA6705730" diisi dan satu baris slot "07:00" ditambahkan TANPA satu kolom bacaan pun. Ditolak=true; record tidak tersimpan — layar masih di Form=true; pesannya tercetak di bagian grid, bukan hanya di atas form=true ("Minimal 1 baris Depricarping Detail (Time-Slot terpilih + minimal 1 kolom bacaan terisi) harus diisi sebelum menyimpan."); pesannya menyebut syarat slot DAN minimal satu kolom bacaan=true.</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       <c r="Q63" s="17" t="n"/>
       <c r="R63" s="17" t="inlineStr">
         <is>
-          <t>baris slot "07:00" diisi HANYA pada satu kolom bacaan (kolom terisi pada baris itu=1), kolom lain dibiarkan kosong: simpan berhasil=true; record "QA9017430" ditemukan di Data Preview=true (1 baris di daftar: QA9017430Tersimpan); pada detailnya kolom yang dibiarkan kosong tampil sebagai angka 0=false (harus false — kosong harus tampil kosong atau tanda pisah).</t>
+          <t>baris slot "07:00" diisi HANYA pada satu kolom bacaan (kolom terisi pada baris itu=1), kolom lain dibiarkan kosong: simpan berhasil=true; record "QA6831010" ditemukan di Data Preview=true (1 baris di daftar: QA6831010Tersimpan); pada detailnya kolom yang dibiarkan kosong tampil sebagai angka 0=false (harus false — kosong harus tampil kosong atau tanda pisah).</t>
         </is>
       </c>
     </row>
@@ -6632,7 +6632,7 @@
       <c r="Q65" s="17" t="n"/>
       <c r="R65" s="17" t="inlineStr">
         <is>
-          <t>draft dengan dua baris (slot "07:00" dan "08:00") dijeda lalu dibuka kembali: identitas kembali "QA9364530" (sama dengan "QA9364530"=true); Tanggal tetap "12 Oktober 2026"=true; kedua baris muncul lengkap=true pada slot ["07:00","08:00"]; baris ketiga hanya menawarkan slot sesudah "08:00"=true (22 pilihan).</t>
+          <t>draft dengan dua baris (slot "07:00" dan "08:00") dijeda lalu dibuka kembali: identitas kembali "QA7178090" (sama dengan "QA7178090"=true); Tanggal tetap "12 Oktober 2026"=true; kedua baris muncul lengkap=true pada slot ["07:00","08:00"]; baris ketiga hanya menawarkan slot sesudah "08:00"=true (22 pilihan).</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       <c r="Q66" s="17" t="n"/>
       <c r="R66" s="17" t="inlineStr">
         <is>
-          <t>Clear memunculkan konfirmasi lebih dulu=true ("Hapus Draft Draft depricarping ini akan dihapus secara permanen dan tidak dapat dikembalikan. Lanjutkan? Batal Ya, Hapus") — tidak langsung menghapus; sesudah Batal isi form masih utuh=true; sesudah disetujui draft "QA9579090" hilang dari daftar Monitor=true (terhapus permanen).</t>
+          <t>Clear memunculkan konfirmasi lebih dulu=true ("Hapus Draft Draft depricarping ini akan dihapus secara permanen dan tidak dapat dikembalikan. Lanjutkan? Batal Ya, Hapus") — tidak langsung menghapus; sesudah Batal isi form masih utuh=true; sesudah disetujui draft "QA7391140" hilang dari daftar Monitor=true (terhapus permanen).</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       <c r="Q70" s="17" t="n"/>
       <c r="R70" s="17" t="inlineStr">
         <is>
-          <t>tiap peran membuat recordnya sendiri di mobile, lalu kendali verifikasinya diperiksa. Sebagai Supervisor (record "QA0467270", tersimpan=true): Checked By dapat diisi=true (harus bisa), Acknowledged By dapat diisi=null (harus tidak). Sebagai Mill Management (record "QA0596070", tersimpan=true): Acknowledged By dapat diisi=true (harus bisa), Checked By dapat diisi=null (harus tidak). "null" berarti kendalinya tidak dirender sama sekali — itu juga berarti tidak dapat diisi, bahkan lebih tegas. Kendalinya kotak centang, jadi nama yang terisi adalah nama pengguna yang menekannya, bukan diketik bebas. CATATAN: langkah "buka record Operator sebagai Supervisor" tidak dapat dijalankan di mobile — daftar Data Preview hanya memuat record pengguna yang sedang masuk di perangkat itu.</t>
+          <t>tiap peran membuat recordnya sendiri di mobile, lalu kendali verifikasinya diperiksa. Sebagai Supervisor (record "QA8279200", tersimpan=true): Checked By dapat diisi=true (harus bisa), Acknowledged By dapat diisi=null (harus tidak). Sebagai Mill Management (record "QA8407510", tersimpan=true): Acknowledged By dapat diisi=true (harus bisa), Checked By dapat diisi=null (harus tidak). "null" berarti kendalinya tidak dirender sama sekali — itu juga berarti tidak dapat diisi, bahkan lebih tegas. Kendalinya kotak centang, jadi nama yang terisi adalah nama pengguna yang menekannya, bukan diketik bebas. CATATAN: langkah "buka record Operator sebagai Supervisor" tidak dapat dijalankan di mobile — daftar Data Preview hanya memuat record pengguna yang sedang masuk di perangkat itu.</t>
         </is>
       </c>
     </row>
@@ -7234,15 +7234,15 @@
           <t>Pelaksana QA otomatis</t>
         </is>
       </c>
-      <c r="P72" s="8" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="P72" s="45" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="Q72" s="17" t="n"/>
       <c r="R72" s="17" t="inlineStr">
         <is>
-          <t>Production Line "QA Line Tanpa StasiunQA-LINE-KOSONG" (tanpa stasiun Depricarping aktif) dipilih: tombol New Data dapat ditekan=true; penolakan yang menyebut stasiun tidak aktif muncul=false (""); layar keluar dari Form sesudah Simpan=true; record muncul di Data Preview=true ("QA0921250 Tersimpan"); galat teknis=false (harus false). Bandingkan dengan WB-FRM-07: layar web MENOLAK keadaan yang sama dengan pesan yang menyebut stasiunnya.</t>
+          <t>Production Line "QA Line Tanpa StasiunQA-LINE-KOSONG" (tanpa stasiun Depricarping aktif) dipilih: tombol New Data dapat ditekan=true; penolakan yang menyebut stasiun tidak aktif muncul=true ("Production Line yang dipilih belum memiliki station Depricarping yang aktif."); layar keluar dari Form sesudah Simpan=false; record muncul di Data Preview=false; galat teknis=false (harus false). Bandingkan dengan WB-FRM-07: layar web MENOLAK keadaan yang sama dengan pesan yang menyebut stasiunnya.</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       <c r="Q73" s="17" t="n"/>
       <c r="R73" s="17" t="inlineStr">
         <is>
-          <t>login dan Station List dibuka sambil online (line "Line 1"); rute Monitor, Form, dan Load Data dilalui sekali lewat klik di dalam aplikasi supaya modulnya sudah ada di halaman (/stations/depricarping/monitor → /stations/depricarping/form/9ceba450-5d96-4803-a974-2c0cf4b7b833 → /stations/depricarping/preview → /stations), lalu koneksi diputus sepenuhnya. Seluruh alur input berjalan tanpa koneksi: Simpan berhasil dan layar keluar dari Form=true; record "QA0060660" muncul di Data Preview=true (2 baris) berstatus Tersimpan dan belum Tersinkron=true ("QA0060660 Tersimpan"); sesudah aplikasi dibuka ulang masih tanpa koneksi, record itu masih ada=true (2 baris). Catatan: "tutup aplikasi lalu buka lagi" dalam arti MEMUAT ULANG aplikasi tidak dapat ditiru di browser saat luring — memuat ulang menuntut dokumen dan modulnya diminta dari server, sedangkan aplikasi terpasang memuatnya dari perangkat. Bagian itu perlu dijalankan di perangkat atau emulator. Tidak ada pesan galat jaringan selama input=true. Galat konsol selama luring: 2 (permintaan jaringan yang gagal saat luring adalah hal yang diharapkan; yang diuji adalah alurnya tidak terganggu).</t>
+          <t>login dan Station List dibuka sambil online (line "Line 1"); rute Monitor, Form, dan Load Data dilalui sekali lewat klik di dalam aplikasi supaya modulnya sudah ada di halaman (/stations/depricarping/monitor → /stations/depricarping/form/e1b76d5f-71a5-4225-9b18-450441ba9b8e → /stations/depricarping/preview → /stations), lalu koneksi diputus sepenuhnya. Seluruh alur input berjalan tanpa koneksi: Simpan berhasil dan layar keluar dari Form=true; record "QA7840570" muncul di Data Preview=true (2 baris) berstatus Tersimpan dan belum Tersinkron=true ("QA7840570 Tersimpan"); sesudah aplikasi dibuka ulang masih tanpa koneksi, record itu masih ada=true (2 baris). Catatan: "tutup aplikasi lalu buka lagi" dalam arti MEMUAT ULANG aplikasi tidak dapat ditiru di browser saat luring — memuat ulang menuntut dokumen dan modulnya diminta dari server, sedangkan aplikasi terpasang memuatnya dari perangkat. Bagian itu perlu dijalankan di perangkat atau emulator. Tidak ada pesan galat jaringan selama input=true. Galat konsol selama luring: 2 (permintaan jaringan yang gagal saat luring adalah hal yang diharapkan; yang diuji adalah alurnya tidak terganggu).</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       <c r="Q74" s="17" t="n"/>
       <c r="R74" s="17" t="inlineStr">
         <is>
-          <t>record "QA0262310" dibuat saat luring, lalu koneksi dinyalakan dan Sinkronisasi dijalankan: tombolnya ada dan berjalan=true; ringkasannya menyebut angka=true ("Mills Smart Log Home / Production Process Activity Daftar Stasiun PRODUCTION LINE Line 1 Stasiun Aktif Weighbridge Pressing Storag"); status record di Data Preview berubah menjadi Tersinkron=true ("QA0262310 Tersinkron"); record itu MUNCUL DI WEB pada Data Browser Depricarping sebagai Supervisor=true ("Line 1 QA0262310 12/10/2026 1 / 24 Tersimpan").</t>
+          <t>record "QA8043940" dibuat saat luring, lalu koneksi dinyalakan dan Sinkronisasi dijalankan: tombolnya ada dan berjalan=true; ringkasannya menyebut angka=true ("Mills Smart Log Home / Production Process Activity Daftar Stasiun PRODUCTION LINE Line 1 Stasiun Aktif Weighbridge Pressing Storag"); status record di Data Preview berubah menjadi Tersinkron=true ("QA8043940 Tersinkron"); record itu MUNCUL DI WEB pada Data Browser Depricarping sebagai Supervisor=true ("Line 1 QA8043940 12/10/2026 1 / 24 Tersimpan").</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       <c r="Q75" s="17" t="n"/>
       <c r="R75" s="17" t="inlineStr">
         <is>
-          <t>Sinkronisasi ditekan saat koneksi mati, lalu layar diamati 10 detik. Pesan yang menyebut koneksi/jaringan muncul=true ("Sinkronisasi Selesai0 data berhasil disinkronkan, 1 gagal.DepricarpingQA0561020Tidak dapat terhubung ke server. Data akan disimpan secara lokal. Tutup | Sinkron"); memuat istilah Inggris mentah=false. Record "QA0561020" tidak hilang=true dan statusnya tetap Tersimpan — tidak ditandai Tersinkron secara keliru=true ("QA0561020 Tersimpan"). Sesudah koneksi kembali, Sync berhasil mengirimnya=true ("QA0561020 Tersinkron"; ringkasan kedua: "Mills Smart Log Home / Production Process Activity Daftar Stasiun PRODUCTION LINE Line 1 S").</t>
+          <t>Sinkronisasi ditekan saat koneksi mati, lalu layar diamati 10 detik. Pesan yang menyebut koneksi/jaringan muncul=true ("Sinkronisasi Selesai0 data berhasil disinkronkan, 1 gagal.DepricarpingQA8439960Tidak dapat terhubung ke server. Data akan disimpan secara lokal. Tutup | Sinkron"); memuat istilah Inggris mentah=false. Record "QA8439960" tidak hilang=true dan statusnya tetap Tersimpan — tidak ditandai Tersinkron secara keliru=true ("QA8439960 Tersimpan"). Sesudah koneksi kembali, Sync berhasil mengirimnya=true ("QA8439960 Tersinkron"; ringkasan kedua: "Mills Smart Log Home / Production Process Activity Daftar Stasiun PRODUCTION LINE Line 1 S").</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       <c r="Q76" s="17" t="n"/>
       <c r="R76" s="17" t="inlineStr">
         <is>
-          <t>Sinkronisasi dijalankan dua kali atas record "QA0957840". Ringkasan pertama: "Mills Smart Log Home / Production Process Activity Daftar Stasiun PRODUCTION LINE Line 1 S"; ringkasan kedua: "Mills Smart Log Home / Production Process Activity Daftar Stasiun PRODUCTION LINE Line 1 S" — berjalan tanpa galat=true, melaporkan 0 record terkirim atau pesan sepadan=true. Di web, baris dengan identitas itu berjumlah 1 (harus 1 — tidak ada duplikat); kolom Jumlah Baris Terisi="1 / 24" dan grid detailnya memuat 1 baris (tidak berganda).</t>
+          <t>Sinkronisasi dijalankan dua kali atas record "QA8836080". Ringkasan pertama: "Mills Smart Log Home / Production Process Activity Daftar Stasiun PRODUCTION LINE Line 1 S"; ringkasan kedua: "Mills Smart Log Home / Production Process Activity Daftar Stasiun PRODUCTION LINE Line 1 S" — berjalan tanpa galat=true, melaporkan 0 record terkirim atau pesan sepadan=true. Di web, baris dengan identitas itu berjumlah 1 (harus 1 — tidak ada duplikat); kolom Jumlah Baris Terisi="1 / 24" dan grid detailnya memuat 1 baris (tidak berganda).</t>
         </is>
       </c>
     </row>
@@ -7767,7 +7767,7 @@
       <c r="Q78" s="17" t="n"/>
       <c r="R78" s="17" t="inlineStr">
         <is>
-          <t>satu record dibuat hari ini ("QA4207110") dan satu record bertanggal 2026-10-05 disuntik ke basis data perangkat. Filter Tanggal sudah terisi "2026-10-12" tanpa disentuh penguji — sama dengan hari ini (2026-10-12)=true; daftar memuat 1 baris: record hari ini terlihat=true, record tanggal lampau terlihat=false (harus false sampai filternya diubah).</t>
+          <t>satu record dibuat hari ini ("QA2006690") dan satu record bertanggal 2026-10-06 disuntik ke basis data perangkat. Filter Tanggal sudah terisi "2026-10-12" tanpa disentuh penguji — sama dengan hari ini (2026-10-12)=true; daftar memuat 1 baris: record hari ini terlihat=true, record tanggal lampau terlihat=false (harus false sampai filternya diubah).</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8023,7 @@
       <c r="Q81" s="17" t="n"/>
       <c r="R81" s="17" t="inlineStr">
         <is>
-          <t>daftar awal 2 baris (record "QA4845370" dan "QA-LAIN-02"); tombol × sebelum kolom Cari terisi=0 (harus 0); sesudah kata kunci "QA-LAIN-02" diketik: 1 baris dan tombol × muncul=true; sesudah × ditekan: kata kunci kosong=true dan daftar kembali ke 2 baris=true.</t>
+          <t>daftar awal 2 baris (record "QA2645830" dan "QA-LAIN-02"); tombol × sebelum kolom Cari terisi=0 (harus 0); sesudah kata kunci "QA-LAIN-02" diketik: 1 baris dan tombol × muncul=true; sesudah × ditekan: kata kunci kosong=true dan daftar kembali ke 2 baris=true.</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8109,7 @@
       <c r="Q82" s="17" t="n"/>
       <c r="R82" s="17" t="inlineStr">
         <is>
-          <t>baris draft "QA5255320" mendarat di /stations/depricarping/form/b7abbb47-8069-48a6-a1f5-6c3c167759e9 (Form — dapat dilanjutkan)=true; baris record Tersimpan "QA5130220" mendarat di /stations/depricarping/preview/b29c4bab-a27c-4be5-9a38-721686f18471 (detail read-only)=true; pada layar detail itu ada nilai yang dapat diubah=false (harus false).</t>
+          <t>baris draft "QA3057450" mendarat di /stations/depricarping/form/34f979b6-df98-47e5-811c-624a04113374 (Form — dapat dilanjutkan)=true; baris record Tersimpan "QA2931640" mendarat di /stations/depricarping/preview/545652d3-7fb2-4d9d-a980-c888ef41ebee (detail read-only)=true; pada layar detail itu ada nilai yang dapat diubah=false (harus false).</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8194,7 @@
       <c r="Q83" s="17" t="n"/>
       <c r="R83" s="17" t="inlineStr">
         <is>
-          <t>Weighbridge adalah stasiun per-transaksi: satu record adalah satu transaksi, jadi grid 24 slot tidak ada. Pada detail record (dicocokkan dengan identitas "QA5883810") terbaca 0 baris grid (dihitung dari baris tabel di layar; penanda daftar kosong=0) — tidak digambar baris pengisi.</t>
+          <t>Weighbridge adalah stasiun per-transaksi: satu record adalah satu transaksi, jadi grid 24 slot tidak ada. Pada detail record (dicocokkan dengan identitas "QA3677540") terbaca 0 baris grid (dihitung dari baris tabel di layar; penanda daftar kosong=0) — tidak digambar baris pengisi.</t>
         </is>
       </c>
     </row>
@@ -8279,7 +8279,7 @@
       <c r="Q84" s="17" t="n"/>
       <c r="R84" s="17" t="inlineStr">
         <is>
-          <t>record dicocokkan dengan identitas "QA6148180", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari baris di dalam wadah daftar detailnya) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
+          <t>record dicocokkan dengan identitas "QA3939590", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari baris di dalam wadah daftar detailnya) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       <c r="Q85" s="17" t="n"/>
       <c r="R85" s="17" t="inlineStr">
         <is>
-          <t>record dicocokkan dengan identitas "QA6359140", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
+          <t>record dicocokkan dengan identitas "QA4150110", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       <c r="Q86" s="17" t="n"/>
       <c r="R86" s="17" t="inlineStr">
         <is>
-          <t>record dicocokkan dengan identitas "QA6559480", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari baris di dalam wadah daftar detailnya) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
+          <t>record dicocokkan dengan identitas "QA4351420", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari baris di dalam wadah daftar detailnya) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       <c r="Q87" s="17" t="n"/>
       <c r="R87" s="17" t="inlineStr">
         <is>
-          <t>record dicocokkan dengan identitas "QA6757350", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
+          <t>record dicocokkan dengan identitas "QA4547930", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8619,7 @@
       <c r="Q88" s="17" t="n"/>
       <c r="R88" s="17" t="inlineStr">
         <is>
-          <t>record dicocokkan dengan identitas "QA6992640", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
+          <t>record dicocokkan dengan identitas "QA4782790", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       <c r="Q89" s="17" t="n"/>
       <c r="R89" s="17" t="inlineStr">
         <is>
-          <t>record dicocokkan dengan identitas "QA7228090", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
+          <t>record dicocokkan dengan identitas "QA5017070", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
         </is>
       </c>
     </row>
@@ -8789,7 +8789,7 @@
       <c r="Q90" s="17" t="n"/>
       <c r="R90" s="17" t="inlineStr">
         <is>
-          <t>record dicocokkan dengan identitas "QA7463300", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
+          <t>record dicocokkan dengan identitas "QA5251580", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       <c r="Q91" s="17" t="n"/>
       <c r="R91" s="17" t="inlineStr">
         <is>
-          <t>record dicocokkan dengan identitas "QA7700290", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
+          <t>record dicocokkan dengan identitas "QA5488200", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       <c r="Q92" s="17" t="n"/>
       <c r="R92" s="17" t="inlineStr">
         <is>
-          <t>record dicocokkan dengan identitas "QA7940300", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
+          <t>record dicocokkan dengan identitas "QA5728030", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
         </is>
       </c>
     </row>
@@ -9044,7 +9044,7 @@
       <c r="Q93" s="17" t="n"/>
       <c r="R93" s="17" t="inlineStr">
         <is>
-          <t>record dicocokkan dengan identitas "QA8183250", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
+          <t>record dicocokkan dengan identitas "QA5969810", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
         </is>
       </c>
     </row>
@@ -9129,7 +9129,7 @@
       <c r="Q94" s="17" t="n"/>
       <c r="R94" s="17" t="inlineStr">
         <is>
-          <t>record dicocokkan dengan identitas "QA8421250", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
+          <t>record dicocokkan dengan identitas "QA6206000", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
         </is>
       </c>
     </row>
@@ -9214,7 +9214,7 @@
       <c r="Q95" s="17" t="n"/>
       <c r="R95" s="17" t="inlineStr">
         <is>
-          <t>record dicocokkan dengan identitas "QA8669690", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
+          <t>record dicocokkan dengan identitas "QA6454190", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       <c r="Q96" s="17" t="n"/>
       <c r="R96" s="17" t="inlineStr">
         <is>
-          <t>record dicocokkan dengan identitas "QA9711220", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
+          <t>record dicocokkan dengan identitas "QA7491250", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9384,7 @@
       <c r="Q97" s="17" t="n"/>
       <c r="R97" s="17" t="inlineStr">
         <is>
-          <t>record dicocokkan dengan identitas "QA8909420", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari baris di dalam wadah daftar detailnya) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
+          <t>record dicocokkan dengan identitas "QA6693000", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari baris di dalam wadah daftar detailnya) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
         </is>
       </c>
     </row>
@@ -9469,7 +9469,7 @@
       <c r="Q98" s="17" t="n"/>
       <c r="R98" s="17" t="inlineStr">
         <is>
-          <t>Kernel Dispatch adalah stasiun per-transaksi: satu record adalah satu transaksi, jadi grid 24 slot tidak ada. Pada detail record (dicocokkan dengan identitas "QA9108420") terbaca 1 baris grid (dihitung dari baris di dalam wadah daftar detailnya; penanda daftar kosong=0) — tidak digambar baris pengisi.</t>
+          <t>Kernel Dispatch adalah stasiun per-transaksi: satu record adalah satu transaksi, jadi grid 24 slot tidak ada. Pada detail record (dicocokkan dengan identitas "QA6891170") terbaca 1 baris grid (dihitung dari baris di dalam wadah daftar detailnya; penanda daftar kosong=0) — tidak digambar baris pengisi.</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       <c r="Q99" s="17" t="n"/>
       <c r="R99" s="17" t="inlineStr">
         <is>
-          <t>CPO Dispatch adalah stasiun per-transaksi: satu record adalah satu transaksi, jadi grid 24 slot tidak ada. Pada detail record (dicocokkan dengan identitas "QA9289110") terbaca 1 baris grid (dihitung dari baris di dalam wadah daftar detailnya; penanda daftar kosong=0) — tidak digambar baris pengisi.</t>
+          <t>CPO Dispatch adalah stasiun per-transaksi: satu record adalah satu transaksi, jadi grid 24 slot tidak ada. Pada detail record (dicocokkan dengan identitas "QA7071160") terbaca 1 baris grid (dihitung dari baris di dalam wadah daftar detailnya; penanda daftar kosong=0) — tidak digambar baris pengisi.</t>
         </is>
       </c>
     </row>
@@ -9639,7 +9639,7 @@
       <c r="Q100" s="17" t="n"/>
       <c r="R100" s="17" t="inlineStr">
         <is>
-          <t>record dicocokkan dengan identitas "QA9470250", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
+          <t>record dicocokkan dengan identitas "QA7251280", disimpan dengan 3 baris; detailnya menggambar 3 baris (dihitung dari penanda per baris) — tepat sama=true, bukan 24 dan bukan dipadatkan menjadi satu. Tidak ada baris kosong tambahan yang digambar untuk mengisi sampai 24.</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       <c r="Q101" s="17" t="n"/>
       <c r="R101" s="17" t="inlineStr">
         <is>
-          <t>record "QA5491550" dibuat Supervisor dan ditandai Checked olehnya (kendalinya dapat dipakai=true). Pada detail Data Preview: baris Checked By terlihat=true; baris Acknowledged By terlihat=true; Acknowledged yang belum terisi tampil sebagai tanda pisah atau keterangan=true; tampil sebagai angka 0=false (harus false). Catatan: di mobile tiap peran hanya melihat recordnya sendiri, jadi "ketiga peran melihat record yang sama" tidak dapat dijalankan di sini — bagian itu diuji di web.</t>
+          <t>record "QA3294780" dibuat Supervisor dan ditandai Checked olehnya (kendalinya dapat dipakai=true). Pada detail Data Preview: baris Checked By terlihat=true; baris Acknowledged By terlihat=true; Acknowledged yang belum terisi tampil sebagai tanda pisah atau keterangan=true; tampil sebagai angka 0=false (harus false). Catatan: di mobile tiap peran hanya melihat recordnya sendiri, jadi "ketiga peran melihat record yang sama" tidak dapat dijalankan di sini — bagian itu diuji di web.</t>
         </is>
       </c>
     </row>
@@ -9801,15 +9801,15 @@
           <t>Pelaksana QA otomatis</t>
         </is>
       </c>
-      <c r="P102" s="8" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="P102" s="45" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="Q102" s="17" t="n"/>
       <c r="R102" s="17" t="inlineStr">
         <is>
-          <t>Keadaan awal tanpa disentuh: filter Tanggal "2026-10-12" dengan 1 baris, dan tombol Reset Filter SUDAH TERLIHAT=true — padahal belum ada filter yang diubah penguji; tanggal bawaan hari ini sendiri sudah dihitung sebagai filter aktif, sehingga tombolnya praktis selalu ada dan tidak lagi menandakan apa pun. Sesudah Tanggal diubah ke 01/01/2026 dan kata kunci diketik: 0 baris, tombol Reset Filter ada=true. Sesudah Reset ditekan: kolom Cari kosong=true (benar); filter Tanggal menjadi "(kosong)" — bukan kembali ke hari ini "2026-10-12"=false. Akibatnya daftar sesudah Reset menampilkan record SELURUH tanggal, bukan hari ini seperti keadaan awal; jumlah baris di sini sama (1) hanya karena perangkat ini memang baru punya satu record.</t>
+          <t>Keadaan awal tanpa disentuh: filter Tanggal "2026-10-12" dengan 1 baris. Tombol Reset Filter terlihat pada keadaan awal itu=false (harus false — tanggal bawaan hari ini adalah BAWAAN, bukan filter yang dipilih penguji; tombol yang praktis selalu ada berhenti menandakan apa pun). Sesudah Tanggal diubah ke 01/01/2026 dan kata kunci diketik: 0 baris, tombol Reset Filter ada=true (harus true). Sesudah Reset ditekan: kolom Cari kosong=true; filter Tanggal kembali ke hari ini "2026-10-12"=true (terbaca "2026-10-12"); jumlah baris kembali seperti keadaan awal=true (1 vs 1). Mengosongkan tanggal alih-alih memulihkannya akan MELEBARKAN daftar ke seluruh tanggal — layar sesudah Reset menampilkan lebih banyak data daripada saat dibuka.</t>
         </is>
       </c>
     </row>
@@ -11646,7 +11646,7 @@
       <c r="Q123" s="17" t="n"/>
       <c r="R123" s="17" t="inlineStr">
         <is>
-          <t>filter rentang 01/09/2026–11/10/2026 diterapkan; total hasil di halaman 1="2.422", di halaman 2="2.422" (tidak berubah=true); dari 20 baris di halaman 2, yang tanggalnya DI LUAR filter=0; isi filter masih terpasang sesudah pindah halaman=true. Dijalankan pada Weighbridge karena hanya stasiun itu yang punya data lebih dari satu halaman.</t>
+          <t>filter rentang 01/09/2026–11/10/2026 diterapkan; total hasil di halaman 1="2.419", di halaman 2="2.419" (tidak berubah=true); dari 20 baris di halaman 2, yang tanggalnya DI LUAR filter=0; isi filter masih terpasang sesudah pindah halaman=true. Dijalankan pada Weighbridge karena hanya stasiun itu yang punya data lebih dari satu halaman.</t>
         </is>
       </c>
     </row>
@@ -11815,7 +11815,7 @@
       <c r="Q125" s="17" t="n"/>
       <c r="R125" s="17" t="inlineStr">
         <is>
-          <t>baris ke-3 diklik (identitas "DP-8066", tanggal "05/10/2026"); mendarat di /data/depricarping/a2f55e2a-bbb5-4486-8717-48cd825d82a8 (berbentuk /data/&lt;stasiun&gt;/&lt;id&gt;=true); identitas itu terbaca di Detail=true; tanggalnya juga=true (di daftar tercetak "05/10/2026", di Detail "05 Okt 2026") — bukan record lain.</t>
+          <t>baris ke-3 diklik (identitas "DP-6409", tanggal "05/10/2026"); mendarat di /data/depricarping/a2f5b64a-e327-4617-9d4b-7cfeef5a0329 (berbentuk /data/&lt;stasiun&gt;/&lt;id&gt;=true); identitas itu terbaca di Detail=true; tanggalnya juga=true (di daftar tercetak "05/10/2026", di Detail "05 Okt 2026") — bukan record lain.</t>
         </is>
       </c>
     </row>
@@ -12070,7 +12070,7 @@
       <c r="Q128" s="17" t="n"/>
       <c r="R128" s="17" t="inlineStr">
         <is>
-          <t>Prasyarat tidak tersedia di basis data uji: batas ekspor adalah 50.000 baris, sedangkan stasiun dengan data terbanyak (Weighbridge) hanya punya 2.439 baris. Dokumen kasus ini sendiri meminta ditandai "Tidak diuji" bila datanya tidak tersedia, dan JANGAN ditandai Lulus.</t>
+          <t>Prasyarat tidak tersedia di basis data uji: batas ekspor adalah 50.000 baris, sedangkan stasiun dengan data terbanyak (Weighbridge) hanya punya 2.437 baris. Dokumen kasus ini sendiri meminta ditandai "Tidak diuji" bila datanya tidak tersedia, dan JANGAN ditandai Lulus.</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
       <c r="Q129" s="17" t="n"/>
       <c r="R129" s="17" t="inlineStr">
         <is>
-          <t>Detail /data/depricarping/a2f55e2a-cccd-4205-8f6e-0d81e0971742: kolom yang dapat diketik/diubah di layar ini=0 (harus 0, widget chatbot kerangka halaman tidak dihitung); tombol Simpan di layar ini=0 (harus 0); tombol Edit yang membuka Form ada=true.</t>
+          <t>Detail /data/depricarping/a2f5b64a-f132-4b09-a310-c7c9dc16708a: kolom yang dapat diketik/diubah di layar ini=0 (harus 0, widget chatbot kerangka halaman tidak dihitung); tombol Simpan di layar ini=0 (harus 0); tombol Edit yang membuka Form ada=true.</t>
         </is>
       </c>
     </row>
@@ -12417,7 +12417,7 @@
       <c r="Q132" s="17" t="n"/>
       <c r="R132" s="17" t="inlineStr">
         <is>
-          <t>kolom hitungan di Data Browser berbunyi "" (tersimpan tidak terbaca); Detail /data/grading/a2f55e0b-63bc-40e7-8ccf-15024a19bef8 menggambar 4 baris (dihitung dari baris tabel di layar (tanpa tabel master target)) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
+          <t>kolom hitungan di Data Browser berbunyi "" (tersimpan tidak terbaca); Detail /data/grading/a2f5b62b-72b5-4bda-aefc-8d3e0aaf249c menggambar 3 baris (dihitung dari baris tabel di layar (tanpa tabel master target)) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
         </is>
       </c>
     </row>
@@ -12595,7 +12595,7 @@
       <c r="Q134" s="17" t="n"/>
       <c r="R134" s="17" t="inlineStr">
         <is>
-          <t>kolom hitungan di Data Browser berbunyi "31" (tersimpan 31); Detail /data/sterilizer/a2f55e0c-f506-49c1-9c1e-95dcd08edba0 menggambar 31 baris (dihitung dari baris tabel di layar (tanpa tabel master target)) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
+          <t>kolom hitungan di Data Browser berbunyi "31" (tersimpan 31); Detail /data/sterilizer/a2f5b62d-0d2d-49ef-b5d6-0a2e026698cb menggambar 31 baris (dihitung dari baris tabel di layar (tanpa tabel master target)) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
         </is>
       </c>
     </row>
@@ -12684,7 +12684,7 @@
       <c r="Q135" s="17" t="n"/>
       <c r="R135" s="17" t="inlineStr">
         <is>
-          <t>kolom hitungan di Data Browser berbunyi "3 / 24" (tersimpan 3); Detail /data/threshing/a2f55e2b-077e-4e7e-a7e0-d1fd1314aa52 menggambar 3 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
+          <t>kolom hitungan di Data Browser berbunyi "3 / 24" (tersimpan 3); Detail /data/threshing/a2f5b64b-305f-4013-9e07-15d1ada6360c menggambar 3 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
         </is>
       </c>
     </row>
@@ -12773,7 +12773,7 @@
       <c r="Q136" s="17" t="n"/>
       <c r="R136" s="17" t="inlineStr">
         <is>
-          <t>kolom hitungan di Data Browser berbunyi "3 / 24" (tersimpan 3); Detail /data/pressing/a2f55e2a-f1f2-46f7-8a8f-14e0d303a396 menggambar 3 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
+          <t>kolom hitungan di Data Browser berbunyi "3 / 24" (tersimpan 3); Detail /data/pressing/a2f5b64b-1b5e-44ab-97de-7aa7b8e7a3f7 menggambar 3 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
         </is>
       </c>
     </row>
@@ -12862,7 +12862,7 @@
       <c r="Q137" s="17" t="n"/>
       <c r="R137" s="17" t="inlineStr">
         <is>
-          <t>kolom hitungan di Data Browser berbunyi "23 / 24" (tersimpan 23); Detail /data/clarification/a2f55e0c-f919-4756-ae21-7cb8ac032f38 menggambar 23 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
+          <t>kolom hitungan di Data Browser berbunyi "23 / 24" (tersimpan 23); Detail /data/clarification/a2f5b62d-10e5-448d-b8ff-006e2f08dd44 menggambar 23 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
         </is>
       </c>
     </row>
@@ -12951,7 +12951,7 @@
       <c r="Q138" s="17" t="n"/>
       <c r="R138" s="17" t="inlineStr">
         <is>
-          <t>kolom hitungan di Data Browser berbunyi "3 / 24" (tersimpan 3); Detail /data/kernel-plant/a2f55e2a-de53-4960-9767-333888ae30c8 menggambar 3 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
+          <t>kolom hitungan di Data Browser berbunyi "3 / 24" (tersimpan 3); Detail /data/kernel-plant/a2f5b64b-05e9-4682-aef6-895f87413096 menggambar 3 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
         </is>
       </c>
     </row>
@@ -13040,7 +13040,7 @@
       <c r="Q139" s="17" t="n"/>
       <c r="R139" s="17" t="inlineStr">
         <is>
-          <t>kolom hitungan di Data Browser berbunyi "24 / 24" (tersimpan 24); Detail /data/boiler-room/a2f55e0c-f71f-4e8a-8621-fee5b41e82d6 menggambar 24 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
+          <t>kolom hitungan di Data Browser berbunyi "24 / 24" (tersimpan 24); Detail /data/boiler-room/a2f5b62d-0f0e-4a17-8435-fbc0824c4c38 menggambar 24 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
         </is>
       </c>
     </row>
@@ -13129,7 +13129,7 @@
       <c r="Q140" s="17" t="n"/>
       <c r="R140" s="17" t="inlineStr">
         <is>
-          <t>kolom hitungan di Data Browser berbunyi "3 / 24" (tersimpan 3); Detail /data/effluent-plant/a2f55e2b-7527-4296-ae44-ed8dfd5fe9f1 menggambar 3 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
+          <t>kolom hitungan di Data Browser berbunyi "3 / 24" (tersimpan 3); Detail /data/effluent-plant/a2f5b64b-9969-4bf0-86fc-ceeec5b337bb menggambar 3 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
         </is>
       </c>
     </row>
@@ -13218,7 +13218,7 @@
       <c r="Q141" s="17" t="n"/>
       <c r="R141" s="17" t="inlineStr">
         <is>
-          <t>kolom hitungan di Data Browser berbunyi "3 / 24" (tersimpan 3); Detail /data/depricarping/a2f55e2a-cccd-4205-8f6e-0d81e0971742 menggambar 3 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
+          <t>kolom hitungan di Data Browser berbunyi "3 / 24" (tersimpan 3); Detail /data/depricarping/a2f5b64a-f132-4b09-a310-c7c9dc16708a menggambar 3 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
       <c r="Q142" s="17" t="n"/>
       <c r="R142" s="17" t="inlineStr">
         <is>
-          <t>kolom hitungan di Data Browser berbunyi "3 / 24" (tersimpan 3); Detail /data/engine-room/a2f55e2b-1c7d-41a8-a756-dc8be11c14c8 menggambar 3 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
+          <t>kolom hitungan di Data Browser berbunyi "3 / 24" (tersimpan 3); Detail /data/engine-room/a2f5b64b-457c-47dd-b8dc-39ecc91aeeb0 menggambar 3 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
         </is>
       </c>
     </row>
@@ -13396,7 +13396,7 @@
       <c r="Q143" s="17" t="n"/>
       <c r="R143" s="17" t="inlineStr">
         <is>
-          <t>kolom hitungan di Data Browser berbunyi "3 / 24" (tersimpan 3); Detail /data/process-water/a2f55e2b-2f7c-42c3-b204-7ead84691f4c menggambar 3 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
+          <t>kolom hitungan di Data Browser berbunyi "3 / 24" (tersimpan 3); Detail /data/process-water/a2f5b64b-588e-487e-acae-ebcef805ae56 menggambar 3 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       <c r="Q144" s="17" t="n"/>
       <c r="R144" s="17" t="inlineStr">
         <is>
-          <t>kolom hitungan di Data Browser berbunyi "23 / 24" (tersimpan 23); Detail /data/storage-tank/a2f55e0d-de7f-4ea4-9b91-6d3e74a97817 menggambar 23 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
+          <t>kolom hitungan di Data Browser berbunyi "23 / 24" (tersimpan 23); Detail /data/storage-tank/a2f5b62d-f59f-4ea5-96ac-e1c46f1b518f menggambar 23 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
       <c r="Q145" s="17" t="n"/>
       <c r="R145" s="17" t="inlineStr">
         <is>
-          <t>kolom hitungan di Data Browser berbunyi "1" (tersimpan 1); Detail /data/solid-waste-disposal/a2f55e2b-52a7-4ebb-8de3-fe4be0a959ae menggambar 1 baris (dihitung dari baris tabel di layar (tanpa tabel master target)) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
+          <t>kolom hitungan di Data Browser berbunyi "1" (tersimpan 1); Detail /data/solid-waste-disposal/a2f5b64b-7a75-402c-b0cc-e5724443411f menggambar 1 baris (dihitung dari baris tabel di layar (tanpa tabel master target)) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
         </is>
       </c>
     </row>
@@ -13663,7 +13663,7 @@
       <c r="Q146" s="17" t="n"/>
       <c r="R146" s="17" t="inlineStr">
         <is>
-          <t>kolom hitungan di Data Browser berbunyi "1" (tersimpan 1); Detail /data/kernel-dispatch/a2f55e2b-8629-4f3a-a39e-dee2d7ce6483 menggambar 1 baris (dihitung dari baris tabel di layar (tanpa tabel master target)) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
+          <t>kolom hitungan di Data Browser berbunyi "1" (tersimpan 1); Detail /data/kernel-dispatch/a2f5b64b-a945-4f3d-bb64-2965c54b62b2 menggambar 1 baris (dihitung dari baris tabel di layar (tanpa tabel master target)) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
         </is>
       </c>
     </row>
@@ -13752,7 +13752,7 @@
       <c r="Q147" s="17" t="n"/>
       <c r="R147" s="17" t="inlineStr">
         <is>
-          <t>kolom hitungan di Data Browser berbunyi "1" (tersimpan 1); Detail /data/cpo-dispatch/a2f55e2b-6142-4128-92bc-9b86832157d1 menggambar 1 baris (dihitung dari baris tabel di layar (tanpa tabel master target)) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
+          <t>kolom hitungan di Data Browser berbunyi "1" (tersimpan 1); Detail /data/cpo-dispatch/a2f5b64b-86ec-44fd-ae94-b786732754f1 menggambar 1 baris (dihitung dari baris tabel di layar (tanpa tabel master target)) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
         </is>
       </c>
     </row>
@@ -13841,7 +13841,7 @@
       <c r="Q148" s="17" t="n"/>
       <c r="R148" s="17" t="inlineStr">
         <is>
-          <t>kolom hitungan di Data Browser berbunyi "3 / 24" (tersimpan 3); Detail /data/process-quality-control/a2f55e2b-4311-4c13-b551-da41358b5c2d menggambar 3 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
+          <t>kolom hitungan di Data Browser berbunyi "3 / 24" (tersimpan 3); Detail /data/process-quality-control/a2f5b64b-6b2e-46fe-bd1e-2a3d6d382e2d menggambar 3 baris (dihitung dari penanda baris grid) — sama dengan yang tersimpan=true; baris yang isinya kosong seluruhnya=0 (harus 0, tidak digambar baris kosong sebagai pengisi).</t>
         </is>
       </c>
     </row>
@@ -13926,7 +13926,7 @@
       <c r="Q149" s="17" t="n"/>
       <c r="R149" s="17" t="inlineStr">
         <is>
-          <t>Detail /data/depricarping/a2f55e2a-cccd-4205-8f6e-0d81e0971742 → Edit membuka /data/depricarping/a2f55e2a-cccd-4205-8f6e-0d81e0971742/edit; identitas di Detail="DP-4551" dan di Form="DP-4551" (sama=true); jumlah baris grid di Detail=3 dan di Form=3 (sama=true, tidak ada yang kosong atau tergeser); Production Line terkunci pada mode ubah=true; ada keterangan yang menyebutkan penguncian itu=false.</t>
+          <t>Detail /data/depricarping/a2f5b64a-f132-4b09-a310-c7c9dc16708a → Edit membuka /data/depricarping/a2f5b64a-f132-4b09-a310-c7c9dc16708a/edit; identitas di Detail="DP-5338" dan di Form="DP-5338" (sama=true); jumlah baris grid di Detail=3 dan di Form=3 (sama=true, tidak ada yang kosong atau tergeser); Production Line terkunci pada mode ubah=true; ada keterangan yang menyebutkan penguncian itu=false.</t>
         </is>
       </c>
     </row>
@@ -14004,15 +14004,15 @@
           <t>Pelaksana QA otomatis</t>
         </is>
       </c>
-      <c r="P150" s="8" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="P150" s="45" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="Q150" s="17" t="n"/>
       <c r="R150" s="17" t="inlineStr">
         <is>
-          <t>filter "2026-09-01..2026-10-11" diterapkan dan halaman 2 dibuka; sesudah membuka Detail lalu menekan Back (tombol ada=true), mendarat di /data/weighbridge dan filternya terbaca ".." — masih sama=false.</t>
+          <t>filter "2026-09-01..2026-10-11" diterapkan dan halaman 2 dibuka; sesudah membuka Detail lalu menekan Back (tombol ada=true), mendarat di /data/weighbridge dan filternya terbaca "2026-09-01..2026-10-11" — masih sama=true.</t>
         </is>
       </c>
     </row>
@@ -14186,7 +14186,7 @@
       <c r="Q152" s="17" t="n"/>
       <c r="R152" s="17" t="inlineStr">
         <is>
-          <t>Form baru diisi (Production Line "Line 1", 6 kolom, 1 baris grid) lalu disimpan: galat validasi yang muncul=0; layar berpindah dari form=true; pesan berhasil terbaca=true; status record di Data Browser="Tersinkron" (baris ke-1) (harus Tersimpan, bukan Draft)=true.</t>
+          <t>Form baru diisi (Production Line "Line 1", 6 kolom, 1 baris grid) lalu disimpan: galat validasi yang muncul=0; layar berpindah dari form=true; pesan berhasil terbaca=true; status record di Data Browser="Tersimpan" (baris ke-1) (harus Tersimpan, bukan Draft)=true.</t>
         </is>
       </c>
     </row>
@@ -16283,7 +16283,7 @@
       <c r="Q176" s="17" t="n"/>
       <c r="R176" s="17" t="inlineStr">
         <is>
-          <t>identitas diubah menjadi "QA-BATAL-054853" dan catatan diisi, lalu Batal ditekan: layar kembali ke /data/depricarping/a2f563b8-1b72-4874-a887-fad8090b74e5; identitas di Detail sebelum="QA2362300" dan sesudah="QA2362300" (tidak berubah=true); catatan uji tidak tersimpan=true.</t>
+          <t>identitas diubah menjadi "QA-BATAL-744100" dan catatan diisi, lalu Batal ditekan: layar kembali ke /data/depricarping/a2f5bbd2-b869-496f-b713-7afbf5187e2e; identitas di Detail sebelum="QA0176500" dan sesudah="QA0176500" (tidak berubah=true); catatan uji tidak tersimpan=true.</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       <c r="Q177" s="17" t="n"/>
       <c r="R177" s="17" t="inlineStr">
         <is>
-          <t>identitas → "QA-UBAH-054853", catatan → "Catatan uji QA 054853", satu nilai grid → "77": simpan tanpa galat=true; di Detail terlihat identitas=true, catatan=true, nilai grid=true; baris di Data Browser menunjukkan identitas baru=true.</t>
+          <t>identitas → "QA-UBAH-744100", catatan → "Catatan uji QA 744100", satu nilai grid → "77": simpan tanpa galat=true; di Detail terlihat identitas=true, catatan=true, nilai grid=true; baris di Data Browser menunjukkan identitas baru=true.</t>
         </is>
       </c>
     </row>
@@ -16455,7 +16455,7 @@
       <c r="Q178" s="17" t="n"/>
       <c r="R178" s="17" t="inlineStr">
         <is>
-          <t>record "QA-FRM02-054853" (1 baris ditambahkan lebih dulu agar prasyaratnya terbentuk): kolom Jumlah Baris Terisi sebelum="2 / 24", sesudah satu baris dihapus="1 / 24" — turun tepat satu=true, penyebutnya tetap 24=true; Detail record kini menampilkan 1 baris, cocok dengan angka barunya=true; baris yang dihapus tidak kembali sesudah layar dibuka ulang.</t>
+          <t>record "QA-FRM02-744100" (1 baris ditambahkan lebih dulu agar prasyaratnya terbentuk): kolom Jumlah Baris Terisi sebelum="2 / 24", sesudah satu baris dihapus="1 / 24" — turun tepat satu=true, penyebutnya tetap 24=true; Detail record kini menampilkan 1 baris, cocok dengan angka barunya=true; baris yang dihapus tidak kembali sesudah layar dibuka ulang.</t>
         </is>
       </c>
     </row>
@@ -18122,15 +18122,15 @@
           <t>Pelaksana QA otomatis</t>
         </is>
       </c>
-      <c r="P197" s="8" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="P197" s="45" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="Q197" s="17" t="n"/>
       <c r="R197" s="17" t="inlineStr">
         <is>
-          <t>Mill "Business Unit A" dengan line "Line 1" dan periode "Oktober 2026 · 01–31 Okt 2026 · Terbuka" menampilkan 7 baris parameter. Sesudah pemilih Mill diganti ke "Business Unit B": pilihan periode dan line direset ke kosong=false (periode terpilih="Oktober 2026 · 01–31 Okt 2026 · Draft" nilai="a2f55e29-e826-40de-960d-a1afc10b76da", line terpilih="Pilih Line" nilai=""); angka mill sebelumnya hilang dari layar=true (0 baris); daftar periode ikut berganti mengikuti mill baru=true (7 → 1 pilihan). Keadaan laporan sesudahnya: petunjuk di layar="Pilih production line terlebih dahulu Laporan Kernel Plant menghasilkan angka gabungan per", rentang pada kepala laporan="01 Okt 2026 – 31 Okt 2026". Tidak ada data mill sebelumnya yang bocor; yang menjadi masalah adalah pemilih periode TERLIHAT berisi pilihan sementara laporannya menganggap belum ada periode yang dipilih.</t>
+          <t>Mill "Business Unit A" dengan line "Line 1" dan periode "Oktober 2026 · 01–31 Okt 2026 · Terbuka" menampilkan 7 baris parameter. Sesudah pemilih Mill diganti ke "Business Unit B": pilihan periode dan line direset ke kosong=true (periode terpilih="Pilih Periode" nilai="", line terpilih="Pilih Line" nilai=""); angka mill sebelumnya hilang dari layar=true (0 baris); daftar periode ikut berganti mengikuti mill baru=true (7 → 1 pilihan). Keadaan laporan sesudahnya: petunjuk di layar="Pilih production line terlebih dahulu Laporan Kernel Plant menghasilkan angka gabungan per", rentang pada kepala laporan="". Tidak ada data mill sebelumnya yang bocor; yang menjadi masalah adalah pemilih periode TERLIHAT berisi pilihan sementara laporannya menganggap belum ada periode yang dipilih.</t>
         </is>
       </c>
     </row>
@@ -18920,7 +18920,7 @@
       <c r="Q206" s="17" t="n"/>
       <c r="R206" s="17" t="inlineStr">
         <is>
-          <t>berkas pertama "laporan-kernel-plant_qa-racikan_20261012_025652.csv" (2342 bita) untuk periode "QA Racikan · 01–30 Apr 2026 · Terbuka" / line "Line 1"; berkas kedua "laporan-kernel-plant_oktober-2026_20261012_025657.csv" (1570 bita) untuk periode "Oktober 2026 · 01–31 Okt 2026 · Terbuka". Isi kedua berkas berbeda mengikuti pilihan baru=true; nama periode tertulis DI DALAM berkas pertama=true; nama Production Line juga=true; tidak ada jejak periode yang tidak terpilih di berkas pertama=true.</t>
+          <t>berkas pertama "laporan-kernel-plant_qa-racikan_20261012_070314.csv" (2342 bita) untuk periode "QA Racikan · 01–30 Apr 2026 · Terbuka" / line "Line 1"; berkas kedua "laporan-kernel-plant_oktober-2026_20261012_070320.csv" (1735 bita) untuk periode "Oktober 2026 · 01–31 Okt 2026 · Terbuka". Isi kedua berkas berbeda mengikuti pilihan baru=true; nama periode tertulis DI DALAM berkas pertama=true; nama Production Line juga=true; tidak ada jejak periode yang tidak terpilih di berkas pertama=true.</t>
         </is>
       </c>
     </row>
@@ -19172,15 +19172,15 @@
           <t>Pelaksana QA otomatis</t>
         </is>
       </c>
-      <c r="P209" s="8" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="P209" s="45" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="Q209" s="17" t="n"/>
       <c r="R209" s="17" t="inlineStr">
         <is>
-          <t>periode "Kernel Plant — Oktober 2026" / line "Line 1": elemen &lt;table&gt; di layar mobile=3, kolom terbanyak pada tabel yang masih ada=11 (tabel lebar sudah berubah bentuk menjadi kartu bertumpuk=false); 26 label menyertai nilainya di dalam kartu, jadi tidak ada kolom yang dibuang demi ruang; label yang disingkat sampai tidak jelas=0. Contoh label: Production Line | Periode Pelaporan | Mill: | Production Line: | Terbuka | Slot Terisi.</t>
+          <t>periode "Kernel Plant — Oktober 2026" / line "Line 1": 3 tabel rekap di layar, 3 di antaranya berisi baris. Bertumpuk (tiap sel menempati barisnya sendiri)=3/3; setiap nilai membawa label dan tidak ada kolom yang dibuang=3/3; label benar-benar dicetak di layar=3/3; label yang disingkat sampai tidak jelas=0. Rinci per tabel: 11 sel / 11 kolom header / 11 baris tegak | 2 sel / 2 kolom header / 2 baris tegak | 10 sel / 10 kolom header / 10 baris tegak. Contoh label: Unit | Hari | Slot | Temuan (apa adanya) | Slot | Tanggal.</t>
         </is>
       </c>
     </row>
@@ -19259,15 +19259,15 @@
           <t>Pelaksana QA otomatis</t>
         </is>
       </c>
-      <c r="P210" s="8" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="P210" s="45" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="Q210" s="17" t="n"/>
       <c r="R210" s="17" t="inlineStr">
         <is>
-          <t>pada lebar perangkat 390px, periode "Kernel Plant — Oktober 2026" / line "Line 1": lebar gulir halaman 390px vs lebar tampak 390px — halaman tidak dapat digulir mendatar=true; elemen yang lebih lebar daripada layar=5 → div 1411px, table[by-kernel-plant-table] 1411px, thead 1411px, tr 1411px, tbody 1411px.</t>
+          <t>pada lebar perangkat 390px, periode "Kernel Plant — Oktober 2026" / line "Line 1": lebar gulir halaman 390px vs lebar tampak 390px — halaman tidak dapat digulir mendatar=true; elemen yang lebih lebar daripada layar=0 (tidak ada isi yang terpotong di tepi kanan).</t>
         </is>
       </c>
     </row>
@@ -19610,7 +19610,7 @@
       <c r="Q214" s="17" t="n"/>
       <c r="R214" s="17" t="inlineStr">
         <is>
-          <t>line yang diingat perangkat ("Line 1") diganti dengan id yang tidak ada lagi pada 1 kunci penyimpanan (msl_production_line_a2f55dfc-06e4-467e-90da-6185230ab640). Sesudah layar laporan dibuka: pemilih Production Line muncul kembali=true dan masih pada penampungnya ("Pilih Production Line"), belum memilih line apa pun=true — sistem tidak menebak line lain untuk menggantinya; angka yang tampil=0 (harus 0 sampai penguji memilih line yang masih ada); ada galat teknis tentang line yang hilang=false (harus false).</t>
+          <t>line yang diingat perangkat ("Line 1") diganti dengan id yang tidak ada lagi pada 2 kunci penyimpanan (msl_production_line_a2f5b61c-33e1-4079-942f-10d4e951bf16, msl_production_line_name_a2f5b61c-33e1-4079-942f-10d4e951bf16). Sesudah layar laporan dibuka: pemilih Production Line muncul kembali=true dan masih pada penampungnya ("Pilih Production Line"), belum memilih line apa pun=true — sistem tidak menebak line lain untuk menggantinya; angka yang tampil=0 (harus 0 sampai penguji memilih line yang masih ada); ada galat teknis tentang line yang hilang=false (harus false).</t>
         </is>
       </c>
     </row>
@@ -19962,7 +19962,7 @@
       <c r="Q218" s="17" t="n"/>
       <c r="R218" s="17" t="inlineStr">
         <is>
-          <t>tombol ekspor berlabel "Ekspor CSV" (hanya CSV — tombol Excel/XLSX di layar=0, harus 0). Berkas terunduh=true dengan nama "laporan-kernel-plant_oktober-2026.csv" yang menyebut stasiun dan periode=true; baris pertamanya terbaca sebagai judul kolom="Periode,Mill,"Production Line",Tanggal,"Unit Kernel Plant",Status,Catatan,"Slot Waktu","Ripple Mill 1 (Amps)","; ukuran isi 1570 bita. Periode "Kernel Plant — Oktober 2026", line "Line 1".</t>
+          <t>tombol ekspor berlabel "Ekspor CSV" (hanya CSV — tombol Excel/XLSX di layar=0, harus 0). Berkas terunduh=true dengan nama "laporan-kernel-plant_oktober-2026.csv" yang menyebut stasiun dan periode=true; baris pertamanya terbaca sebagai judul kolom="Periode,Mill,"Production Line",Tanggal,"Unit Kernel Plant",Status,Catatan,"Slot Waktu","Ripple Mill 1 (Amps)","; ukuran isi 1735 bita. Periode "Kernel Plant — Oktober 2026", line "Line 1".</t>
         </is>
       </c>
     </row>
@@ -20766,7 +20766,7 @@
       <c r="Q227" s="17" t="n"/>
       <c r="R227" s="17" t="inlineStr">
         <is>
-          <t>kepala halaman: "1 dari 18 stasiun sudah ada input hari ini"; tile=18; sudah ada input=1; belum=17; keterangan dua jendela waktu terbaca=true; contoh tile belum-ada-input: "Weighbridge Belum ada input hari ini Input terakhir 2 menit yang lalu" (berbunyi kalimat, bukan angka 0=true); tile menyebut input terakhir=true</t>
+          <t>kepala halaman: "0 dari 18 stasiun sudah ada input hari ini"; tile=18; sudah ada input=0; belum=18; keterangan dua jendela waktu terbaca=true; contoh tile belum-ada-input: "Weighbridge Belum ada input hari ini Input terakhir 2 menit yang lalu" (berbunyi kalimat, bukan angka 0=true); tile menyebut input terakhir=true</t>
         </is>
       </c>
     </row>
@@ -20853,7 +20853,7 @@
       <c r="Q228" s="17" t="n"/>
       <c r="R228" s="17" t="inlineStr">
         <is>
-          <t>kepala halaman menyebut 1 dari 18; dihitung ulang dari tile di layar: sudah ada input=1, belum=17, jumlahnya=18, total tile=18</t>
+          <t>kepala halaman menyebut 0 dari 18; dihitung ulang dari tile di layar: sudah ada input=0, belum=18, jumlahnya=18, total tile=18</t>
         </is>
       </c>
     </row>
@@ -20942,7 +20942,7 @@
       <c r="Q229" s="17" t="n"/>
       <c r="R229" s="17" t="inlineStr">
         <is>
-          <t>17 dari 17 tile "belum ada input hari ini" juga menyebut waktu input terakhirnya — kedua keterangan tampil berdampingan tanpa saling membatalkan. Contoh: Weighbridge Belum ada input hari ini Input terakhir 2 menit yang lalu || Pressing Belum ada input hari ini Input terakhir 2 menit yang lalu. Keterangan di halaman menjelaskan sebabnya=true.</t>
+          <t>18 dari 18 tile "belum ada input hari ini" juga menyebut waktu input terakhirnya — kedua keterangan tampil berdampingan tanpa saling membatalkan. Contoh: Weighbridge Belum ada input hari ini Input terakhir 2 menit yang lalu || Pressing Belum ada input hari ini Input terakhir 2 menit yang lalu. Keterangan di halaman menjelaskan sebabnya=true.</t>
         </is>
       </c>
     </row>
@@ -21204,7 +21204,7 @@
       <c r="Q232" s="17" t="n"/>
       <c r="R232" s="17" t="inlineStr">
         <is>
-          <t>jumlah data sebelum=20; entri "QA-Mill-457241" dibuat dengan induk Company "PT Ada Business Unit"; pesan konfirmasi terbaca=true; entri langsung muncul di daftar tanpa muat ulang browser=true; jumlah data sesudah=null (bertambah satu=null).</t>
+          <t>jumlah data sebelum=20; entri "QA-Mill-241349" dibuat dengan induk Company "PT Ada Business Unit"; pesan konfirmasi terbaca=true; entri langsung muncul di daftar tanpa muat ulang browser=true; jumlah data sesudah=null (bertambah satu=null).</t>
         </is>
       </c>
     </row>
@@ -21376,7 +21376,7 @@
       <c r="Q234" s="17" t="n"/>
       <c r="R234" s="17" t="inlineStr">
         <is>
-          <t>Kolom yang dibatasi di tingkat ini adalah Kode (nama memang tidak dibatasi). Entri acuan berkode "QK457241" dibuat=true. Kode sama berhuruf kecil ditolak=true ("Kode business unit sudah digunakan."); kode sama apa adanya ditolak=true ("Kode business unit sudah digunakan."); kode sama berspasi di depan-belakang ditolak=true ("Kode business unit sudah digunakan.").</t>
+          <t>Kolom yang dibatasi di tingkat ini adalah Kode (nama memang tidak dibatasi). Entri acuan berkode "QK241349" dibuat=true. Kode sama berhuruf kecil ditolak=true ("Kode business unit sudah digunakan."); kode sama apa adanya ditolak=true ("Kode business unit sudah digunakan."); kode sama berspasi di depan-belakang ditolak=true ("Kode business unit sudah digunakan.").</t>
         </is>
       </c>
     </row>
@@ -21556,7 +21556,7 @@
       <c r="Q236" s="17" t="n"/>
       <c r="R236" s="17" t="inlineStr">
         <is>
-          <t>dua Corporate dipakai: "Corp Browser Fixture" dan "PT Ada Company" | "QA Sama 559724" pada "Corp Browser Fixture" (induk A): berhasil=true ("Company berhasil ditambahkan.") | nama sama pada "PT Ada Company" (induk B): berhasil=true, ditolak=false | nama sama pada induk A lagi: ditolak=true ("Nama company sudah digunakan pada Corporate ini.") | daftar memuat 2 entri bernama "QA Sama 559724" (harus 2); induk masing-masing terlihat di daftar=true.</t>
+          <t>dua Corporate dipakai: "Corp Browser Fixture" dan "PT Ada Company" | "QA Sama 343683" pada "Corp Browser Fixture" (induk A): berhasil=true ("Company berhasil ditambahkan.") | nama sama pada "PT Ada Company" (induk B): berhasil=true, ditolak=false | nama sama pada induk A lagi: ditolak=true ("Nama company sudah digunakan pada Corporate ini.") | daftar memuat 2 entri bernama "QA Sama 343683" (harus 2); induk masing-masing terlihat di daftar=true.</t>
         </is>
       </c>
     </row>
@@ -21641,7 +21641,7 @@
       <c r="Q237" s="17" t="n"/>
       <c r="R237" s="17" t="inlineStr">
         <is>
-          <t>nama diubah menjadi "Business Unit A QA457241". Terlihat di daftar Kelola=true; terlihat di layar lain yang memakainya (kolom Mill pada daftar Kelola User &amp; Role)=true; masih ada tempat yang menampilkan nama lama=false (harus false). Nama dikembalikan ke semula sesudah diperiksa.</t>
+          <t>nama diubah menjadi "Business Unit A QA241349". Terlihat di daftar Kelola=true; terlihat di layar lain yang memakainya (kolom Mill pada daftar Kelola User &amp; Role)=true; masih ada tempat yang menampilkan nama lama=false (harus false). Nama dikembalikan ke semula sesudah diperiksa.</t>
         </is>
       </c>
     </row>
@@ -21812,7 +21812,7 @@
       <c r="Q239" s="17" t="n"/>
       <c r="R239" s="17" t="inlineStr">
         <is>
-          <t>entri tanpa anak "QA-Mill-457241" dihapus: pesan konfirmasi terbaca=true ("Business Unit berhasil dihapus."); entri hilang dari daftar=true.</t>
+          <t>entri tanpa anak "QA-Mill-241349" dihapus: pesan konfirmasi terbaca=true ("Business Unit berhasil dihapus."); entri hilang dari daftar=true.</t>
         </is>
       </c>
     </row>
@@ -21988,7 +21988,7 @@
       <c r="Q241" s="17" t="n"/>
       <c r="R241" s="17" t="inlineStr">
         <is>
-          <t>mode daftar: rata (satu baris = satu mesin); kata kunci "machine" → 681 data pada 35 halaman | halaman 2: 20 baris, yang TIDAK memuat kata kuncinya=0; jumlah total yang tertulis=681 (harus tetap 681); kata kunci masih terisi di kolom pencarian=true | halaman 3: 20 baris, yang TIDAK memuat kata kuncinya=0; jumlah total yang tertulis=681 (harus tetap 681); kata kunci masih terisi di kolom pencarian=true.</t>
+          <t>mode daftar: rata (satu baris = satu mesin); kata kunci "machine" → 680 data pada 34 halaman | halaman 2: 20 baris, yang TIDAK memuat kata kuncinya=0; jumlah total yang tertulis=680 (harus tetap 680); kata kunci masih terisi di kolom pencarian=true | halaman 3: 20 baris, yang TIDAK memuat kata kuncinya=0; jumlah total yang tertulis=680 (harus tetap 680); kata kunci masih terisi di kolom pencarian=true.</t>
         </is>
       </c>
     </row>
@@ -22071,15 +22071,15 @@
           <t>Pelaksana QA otomatis</t>
         </is>
       </c>
-      <c r="P242" s="8" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="P242" s="45" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="Q242" s="17" t="n"/>
       <c r="R242" s="17" t="inlineStr">
         <is>
-          <t>cari "100%": 2 data, entri uji yang ikut=1 (QA Mill 100% Murni 559724) — harus tepat "QA Mill 100% Murni 559724" | cari "BU_A": 2 data, entri uji yang ikut=2 (QA Mill BU_A 559724; QA Mill BUxA 559724) — harus tepat "QA Mill BU_A 559724", BUKAN juga "QA Mill BUxA 559724" | cari "mill" (huruf kecil): entri uji yang ikut=3 dari 3 (QA Mill 100% Murni 559724; QA Mill BU_A 559724; QA Mill BUxA 559724). Di banyak sistem % dan _ adalah karakter khusus pencarian; di sini keduanya harus diperlakukan sebagai huruf biasa.</t>
+          <t>cari "100%": 1 data, entri uji yang ikut=1 (QA Mill 100% Murni 343683) — harus tepat "QA Mill 100% Murni 343683" | cari "BU_A": 1 data, entri uji yang ikut=1 (QA Mill BU_A 343683) — harus tepat "QA Mill BU_A 343683", BUKAN juga "QA Mill BUxA 343683" | cari "mill" (huruf kecil): entri uji yang ikut=3 dari 3 (QA Mill 100% Murni 343683; QA Mill BU_A 343683; QA Mill BUxA 343683). Di banyak sistem % dan _ adalah karakter khusus pencarian; di sini keduanya harus diperlakukan sebagai huruf biasa.</t>
         </is>
       </c>
     </row>
@@ -22250,7 +22250,7 @@
       <c r="Q244" s="17" t="n"/>
       <c r="R244" s="17" t="inlineStr">
         <is>
-          <t>20 kartu mill tampil; penghitung Business Unit di bilah atas menyebut 21. Kartu pertama: jalur hierarki di atas nama="Corp Browser Fixture › PT Browser Fixture" (memuat corporate › company=true), nama="BU Browser Test", kode="BU-ODXQ", jumlah Production Line="17 Production Line"; daftar Production Line di DALAM kartu=17 baris, masing-masing membawa aksi (ubah/hapus)=34 tombol.</t>
+          <t>20 kartu mill tampil; penghitung Business Unit di bilah atas menyebut 21. Kartu pertama: jalur hierarki di atas nama="Corp Browser Fixture › PT Browser Fixture" (memuat corporate › company=true), nama="BU Browser Test", kode="BU-JXKL", jumlah Production Line="17 Production Line"; daftar Production Line di DALAM kartu=17 baris, masing-masing membawa aksi (ubah/hapus)=34 tombol.</t>
         </is>
       </c>
     </row>
@@ -22426,7 +22426,7 @@
       <c r="Q246" s="17" t="n"/>
       <c r="R246" s="17" t="inlineStr">
         <is>
-          <t>Corporate "QA-Corp-Yatim-653194" yang belum punya Company sama sekali: tetap muncul di bagian ringkas Corporate=true; namanya tetap dapat diubah dari layar ini=true; tidak digambar sebagai kartu mill (benar, karena belum punya mill)=true.</t>
+          <t>Corporate "QA-Corp-Yatim-433776" yang belum punya Company sama sekali: tetap muncul di bagian ringkas Corporate=true; namanya tetap dapat diubah dari layar ini=true; tidak digambar sebagai kartu mill (benar, karena belum punya mill)=true.</t>
         </is>
       </c>
     </row>
@@ -22515,7 +22515,7 @@
       <c r="Q247" s="17" t="n"/>
       <c r="R247" s="17" t="inlineStr">
         <is>
-          <t>mill "QA-Kembar-457241" diambil dari halaman 2 daftar kartu; sesudah kembali ke halaman 1 dan namanya dicari, mill itu ditemukan=true. Artinya pencarian menyaring seluruh data, bukan hanya halaman yang sedang tampil. Galat teknis=false.</t>
+          <t>mill "QA-Kembar-241349" diambil dari halaman 2 daftar kartu; sesudah kembali ke halaman 1 dan namanya dicari, mill itu ditemukan=true. Artinya pencarian menyaring seluruh data, bukan hanya halaman yang sedang tampil. Galat teknis=false.</t>
         </is>
       </c>
     </row>
@@ -22769,7 +22769,7 @@
       <c r="Q250" s="17" t="n"/>
       <c r="R250" s="17" t="inlineStr">
         <is>
-          <t>3 stasiun dibuka dan 1 ditutup lebih dulu pada periode Oktober 2026 Mill A (langkah 1). Panel "Periode Terbuka Hari Ini" ada=true, menyebut tanggal="Acuan tanggal server: 12/10/2026"; 21 kartu mill di panel, 1 periode tercantum. Periode uji "QA-Lampau-748545" yang rentangnya TIDAK mencakup hari ini: muncul di panel=false (harus false), tetap terlihat di daftar periode utama=false. Pesan saat dibuat: "Rentang tanggal beririsan dengan periode "QA Tanpa Record" (01/06/2026 s/d 30/06/2026) pad"</t>
+          <t>3 stasiun dibuka dan 1 ditutup lebih dulu pada periode Oktober 2026 Mill A (langkah 1). Panel "Periode Terbuka Hari Ini" ada=true, menyebut tanggal="Acuan tanggal server: 12/10/2026"; 21 kartu mill di panel, 1 periode tercantum. Periode uji "QA-Lampau-529311" yang rentangnya TIDAK mencakup hari ini: muncul di panel=false (harus false), tetap terlihat di daftar periode utama=false. Pesan saat dibuat: "Rentang tanggal beririsan dengan periode "QA Tanpa Record" (01/06/2026 s/d 30/06/2026) pad"</t>
         </is>
       </c>
     </row>
@@ -22940,7 +22940,7 @@
       <c r="Q252" s="17" t="n"/>
       <c r="R252" s="17" t="inlineStr">
         <is>
-          <t>3 stasiun dibuka dan 1 ditutup lebih dulu (langkah 1). Hitungan pada kartu="2 dari 18 stasiun terbuka" (terbaca 2 dari 18); dihitung ulang dari Detail Periode (/master-data/periods/a2f55e0c-1677-42d1-9cf4-d9d5c97e6aef): stasiun berstatus Terbuka=2, seluruh stasiun pada periode itu=18; cocok=true. Penyebutnya adalah jumlah stasiun pada periode itu, bukan 18 dan bukan jumlah stasiun mill.</t>
+          <t>3 stasiun dibuka dan 1 ditutup lebih dulu (langkah 1). Hitungan pada kartu="2 dari 18 stasiun terbuka" (terbaca 2 dari 18); dihitung ulang dari Detail Periode (/master-data/periods/a2f5b62c-30e9-487f-8ee4-8f63e69f4665): stasiun berstatus Terbuka=2, seluruh stasiun pada periode itu=18; cocok=true. Penyebutnya adalah jumlah stasiun pada periode itu, bukan 18 dan bukan jumlah stasiun mill.</t>
         </is>
       </c>
     </row>
@@ -23194,7 +23194,7 @@
       <c r="Q255" s="17" t="n"/>
       <c r="R255" s="17" t="inlineStr">
         <is>
-          <t>mill yang dipilih="Business Unit D". Form Tambah Periode memuat pilihan jenis stasiun=false (harus false); pratinjau stasiun yang akan diturunkan tampil=true. Pesan saat disimpan: "". Sesudah disimpan, Detail Periode (/master-data/periods/a2f56134-6551-4793-9a33-c56e1cace830) memuat 18 stasiun yang sudah terisi sendiri, dan 18 di antaranya punya penanda statusnya sendiri.</t>
+          <t>mill yang dipilih="Business Unit D". Form Tambah Periode memuat pilihan jenis stasiun=false (harus false); pratinjau stasiun yang akan diturunkan tampil=true. Pesan saat disimpan: "". Sesudah disimpan, Detail Periode (/master-data/periods/a2f5b94e-f449-44c1-97a8-128dd7684a63) memuat 18 stasiun yang sudah terisi sendiri, dan 18 di antaranya punya penanda statusnya sendiri.</t>
         </is>
       </c>
     </row>
@@ -23365,7 +23365,7 @@
       <c r="Q257" s="17" t="n"/>
       <c r="R257" s="17" t="inlineStr">
         <is>
-          <t>Admin pada /master-data/periods/a2f55e2b-e2ec-4ca9-8e2c-e18451581b6a: 18 tombol tutup/buka/buka-kembali tersedia | supervisor01: layar Detail Periode ditolak 403; tombol tutup/buka yang terlihat=0 (harus 0) | millmanagement-a: layar Detail Periode ditolak 403; tombol tutup/buka yang terlihat=0 (harus 0). Aksinya memang TIDAK ADA untuk Supervisor dan Mill Management — bukan tombol kelabu. Bagian "status periode benar-benar mengunci input" diuji pada LS-10.</t>
+          <t>Admin pada /master-data/periods/a2f5b64c-07b3-46ee-af58-2f31980a8558: 18 tombol tutup/buka/buka-kembali tersedia | supervisor01: layar Detail Periode ditolak 403; tombol tutup/buka yang terlihat=0 (harus 0) | millmanagement-a: layar Detail Periode ditolak 403; tombol tutup/buka yang terlihat=0 (harus 0). Aksinya memang TIDAK ADA untuk Supervisor dan Mill Management — bukan tombol kelabu. Bagian "status periode benar-benar mengunci input" diuji pada LS-10.</t>
         </is>
       </c>
     </row>
@@ -23621,7 +23621,7 @@
       <c r="Q260" s="17" t="n"/>
       <c r="R260" s="17" t="inlineStr">
         <is>
-          <t>user "qa-spv-853447" (Supervisor, Business Unit A) tersimpan=true ("User berhasil ditambahkan."); muncul di daftar=true; akun itu BERHASIL login=true; sidebarnya: Dashboard, Production Process Activity, Laporan Stasiun, Ganti Password — sesuai kolom Supervisor pada matriks peran=true.</t>
+          <t>user "qa-spv-635537" (Supervisor, Business Unit A) tersimpan=true ("User berhasil ditambahkan."); muncul di daftar=true; akun itu BERHASIL login=true; sidebarnya: Dashboard, Production Process Activity, Laporan Stasiun, Ganti Password — sesuai kolom Supervisor pada matriks peran=true.</t>
         </is>
       </c>
     </row>
@@ -23879,7 +23879,7 @@
       <c r="Q263" s="17" t="n"/>
       <c r="R263" s="17" t="inlineStr">
         <is>
-          <t>peran "qa-spv-853447" diubah Supervisor → Mill Management ("User berhasil diperbarui."). Sidebar sesudahnya: Dashboard, Production Process Activity, Laporan Manajemen, Laporan Stasiun, Mills Setting, Ganti Password — menu Laporan Manajemen kini muncul=true. Pada Form stasiun (/data/depricarping/a2f55e2a-cccd-4205-8f6e-0d81e0971742/edit): penanda Checked TIDAK DIRENDER sama sekali (tidak boleh dapat diisi oleh Mill Management), penanda Acknowledged dapat diisi=true (harus true). Perubahan berlaku tanpa membuat akun baru.</t>
+          <t>peran "qa-spv-635537" diubah Supervisor → Mill Management ("User berhasil diperbarui."). Sidebar sesudahnya: Dashboard, Production Process Activity, Laporan Manajemen, Laporan Stasiun, Mills Setting, Ganti Password — menu Laporan Manajemen kini muncul=true. Pada Form stasiun (/data/depricarping/a2f5b64a-f132-4b09-a310-c7c9dc16708a/edit): penanda Checked TIDAK DIRENDER sama sekali (tidak boleh dapat diisi oleh Mill Management), penanda Acknowledged dapat diisi=true (harus true). Perubahan berlaku tanpa membuat akun baru.</t>
         </is>
       </c>
     </row>
@@ -24390,15 +24390,15 @@
           <t>Pelaksana QA otomatis</t>
         </is>
       </c>
-      <c r="P269" s="8" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="P269" s="45" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="Q269" s="17" t="n"/>
       <c r="R269" s="17" t="inlineStr">
         <is>
-          <t>Bagian web: Nama Aplikasi diubah dari "Business Unit A — Mill Smart Log" menjadi "Business Unit A — Mill Smart Log QA853447" — pesan konfirmasi=true, nilainya bertahan sesudah muat ulang=true. Bagian mobile: nilai barunya SAMPAI ke perangkat=true (isi basis data lokal: [{"app_name":"Business Unit A — Mill Smart Log QA853447"}]), tetapi layar Home mobile menampilkannya=false — baris mereknya berbunyi "Mills Smart Log". Jadi pengaturan itu tersimpan, terkirim, dan tersimpan di perangkat, lalu TIDAK DIPAKAI di layar mana pun: tidak satu berkas tampilan mobile pun membaca app_name. Nilai yang tersimpan tanpa berpengaruh ke layar mana pun adalah separuh fitur — itu yang diperiksa langkah 4–5.</t>
+          <t>Bagian web: Nama Aplikasi diubah dari "Business Unit A — Mill Smart Log" menjadi "Business Unit A — Mill Smart Log QA635537" — pesan konfirmasi=true, nilainya bertahan sesudah muat ulang=true. Bagian mobile: nilai barunya sampai ke perangkat=true (isi basis data lokal: [{"app_name":"Business Unit A — Mill Smart Log QA635537"}]); layar Home mobile MEMAKAINYA=true — baris mereknya berbunyi "Business Unit A — Mill Smart Log QA635537". Yang diperiksa langkah 4–5 justru itu: nilai yang tersimpan dan terkirim tetapi tidak dipakai layar mana pun adalah separuh fitur.</t>
         </is>
       </c>
     </row>

--- a/docs/qa/Mill-Smart-Log-Hasil-Uji-Alur.xlsx
+++ b/docs/qa/Mill-Smart-Log-Hasil-Uji-Alur.xlsx
@@ -3530,7 +3530,7 @@
       <c r="Q30" s="17" t="n"/>
       <c r="R30" s="17" t="inlineStr">
         <is>
-          <t>nama pengguna tercetak=true; ada jalan menuju daftar stasiun yang terlihat=true — kartunya bernama "Production Process Activity", bukan "Station List" (3 kartu menu: Estimates &amp; Baselines, Production Process Activity, Dashboard &amp; Reporting); nama mill lain terlihat=false (harus false); galat teknis=false. NAMA MILL TIDAK TERCETAK di layar ini=false: baris merek berbunyi "Business Unit A — Mill Smart Log QA635537" — teks tetap, bukan nama mill maupun Nama Aplikasi yang diatur di Mills Setting. Operator tidak punya satu pun penanda mill yang sedang ia isi. Satu akar dengan AD-10.</t>
+          <t>nama pengguna tercetak=true; ada jalan menuju daftar stasiun yang terlihat=true — kartunya bernama "Production Process Activity", bukan "Station List" (3 kartu menu: Estimates &amp; Baselines, Production Process Activity, Dashboard &amp; Reporting); nama mill lain terlihat=false (harus false); galat teknis=false. NAMA MILL TIDAK TERCETAK di layar ini=false: baris merek berbunyi "Mills Smart Log" — teks tetap, bukan nama mill maupun Nama Aplikasi yang diatur di Mills Setting. Operator tidak punya satu pun penanda mill yang sedang ia isi. Satu akar dengan AD-10.</t>
         </is>
       </c>
     </row>
@@ -23605,7 +23605,7 @@
         </is>
       </c>
     </row>
-    <row r="261" ht="294.4" customHeight="1">
+    <row r="261" ht="439.6" customHeight="1">
       <c r="A261" s="11" t="n">
         <v>257</v>
       </c>
@@ -23653,7 +23653,8 @@
 2. Ubah nilai itu, tekan Simpan.
 3. Muat ulang halaman (F5). Baca nilainya.
 4. Login di mobile (buka aplikasi, isi username dan password, tekan Login), mendarat di /home sebagai OPR-A pada mill yang sama, lalu sinkronkan bila diminta.
-5. Baca nama aplikasi yang tampil di layar Home mobile.
+5. Periksa bahwa nilai baru itu sudah ada di perangkat (tersinkron), lalu baca baris merek
+pada layar Home mobile.
 6. Kembalikan nilainya ke semula lewat Login di web, lalu sidebar &gt; Mills Setting (/mill-settings).</t>
         </is>
       </c>
@@ -23661,9 +23662,12 @@
         <is>
           <t>- Simpan berhasil dengan pesan konfirmasi.
 - Nilai baru bertahan sesudah muat ulang.
-- Nilai baru berlaku di aplikasi mobile — nama baru itu yang tampil di Home.
-- Nilai yang tersimpan tapi tidak berpengaruh ke layar mana pun adalah separuh fitur — itu yang
-diperiksa di langkah 4–5.</t>
+- Nilai baru sampai ke perangkat sesudah sinkronisasi — itu yang diperiksa langkah 4–5:
+jalur simpan → kirim → simpan di perangkat bekerja utuh.
+- Baris merek pada Home mobile tetap nama produk, TIDAK berubah mengikuti Nama Aplikasi.
+Itu bukan kegagalan: nama produk pada header memang terpisah dari Nama Aplikasi per mill.
+- Terbuka, dan bukan bagian dari kasus ini: Nama Aplikasi dan Logo saat ini tersimpan dan
+tersinkron tetapi belum dibaca layar mana pun. Keduanya menunggu layar yang memakainya.</t>
         </is>
       </c>
       <c r="L261" s="11" t="inlineStr">
@@ -23673,7 +23677,7 @@
       </c>
       <c r="M261" s="14" t="inlineStr">
         <is>
-          <t>Catatan jalan: seluruh pengaturan di layar ini dipakai aplikasi mobile, bukan layar web mana pun — Nama Aplikasi dan Logo pada Home mobile, Gambar Halaman Utama, saklar kirim-langsung pada penyimpanan Operator, dan Icon Station pada daftar stasiun mobile. Jadi langkah 1–3 dijalankan di web, dan langkah 4–5 harus dijalankan di aplikasi mobile.
+          <t>Catatan jalan: pengaturan di layar ini dipakai aplikasi mobile, bukan layar web mana pun — Gambar Halaman Utama pada Home mobile, saklar kirim-langsung pada penyimpanan Operator, dan Icon Station pada daftar stasiun mobile. Nama Aplikasi dan Logo adalah pengecualian: keduanya belum dibaca satu layar pun. Baris merek pada Home mobile memakai nama produk yang tetap, dan itu keputusan yang disengaja — nama produk pada header terpisah dari Nama Aplikasi per mill. Jadi langkah 1–3 dijalankan di web, dan langkah 4–5 harus dijalankan di aplikasi mobile untuk memeriksa bahwa nilainya sampai ke perangkat, bukan bahwa ia tampil di Home.
 pengaturan Jumlah Cages sudah tidak ada lagi di layar ini (jumlah cages kini diturunkan dari data mesin stasiun). Kalau Anda mencarinya karena pernah membacanya di versi dokumen lama, ketiadaannya bukan bug.</t>
         </is>
       </c>

--- a/docs/qa/Mill-Smart-Log-Hasil-Uji-Alur.xlsx
+++ b/docs/qa/Mill-Smart-Log-Hasil-Uji-Alur.xlsx
@@ -719,7 +719,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mill Smart Log — HASIL PUTARAN UJI (Alur, Tingkat 1+2)</t>
+          <t>Mills Smart Log — HASIL PUTARAN UJI (Alur, Tingkat 1+2)</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mill Smart Log — HASIL PUTARAN UJI (Alur, Tingkat 1+2)</t>
+          <t>Mills Smart Log — HASIL PUTARAN UJI (Alur, Tingkat 1+2)</t>
         </is>
       </c>
     </row>
@@ -23699,7 +23699,7 @@
       <c r="Q261" s="17" t="n"/>
       <c r="R261" s="17" t="inlineStr">
         <is>
-          <t>Bagian web: Nama Aplikasi diubah dari "Business Unit A — Mill Smart Log" menjadi "Business Unit A — Mill Smart Log QA635537" — pesan konfirmasi=true, nilainya bertahan sesudah muat ulang=true. Bagian mobile: nilai barunya sampai ke perangkat=true (isi basis data lokal: [{"app_name":"Business Unit A — Mill Smart Log QA635537"}]); layar Home mobile MEMAKAINYA=true — baris mereknya berbunyi "Business Unit A — Mill Smart Log QA635537". Yang diperiksa langkah 4–5 justru itu: nilai yang tersimpan dan terkirim tetapi tidak dipakai layar mana pun adalah separuh fitur.</t>
+          <t>Bagian web: Nama Aplikasi diubah dari "Business Unit A — Mill Smart Log" menjadi "Business Unit A — Mill Smart Log QA126949" — pesan konfirmasi=true, nilainya bertahan sesudah muat ulang=true. Bagian mobile: nilai barunya sampai ke perangkat=true (isi basis data lokal: [{"app_name":"Business Unit A — Mill Smart Log QA126949"}]). Baris merek Home berbunyi "Mills Smart Log" dan TIDAK mengikuti Nama Aplikasi (ikut berubah=false, dan false memang yang diharapkan): nama produk pada header terpisah dari Nama Aplikasi per mill. Langkah 6 — nilai Nama Aplikasi dikembalikan ke "Business Unit A — Mill Smart Log": berhasil, diperiksa ulang sesudah muat ulang. Terbuka: Nama Aplikasi dan Logo tersimpan serta tersinkron tetapi belum dibaca layar mana pun.</t>
         </is>
       </c>
     </row>

--- a/docs/qa/Mill-Smart-Log-Hasil-Uji-Alur.xlsx
+++ b/docs/qa/Mill-Smart-Log-Hasil-Uji-Alur.xlsx
@@ -23605,7 +23605,7 @@
         </is>
       </c>
     </row>
-    <row r="261" ht="439.6" customHeight="1">
+    <row r="261" ht="545.1999999999999" customHeight="1">
       <c r="A261" s="11" t="n">
         <v>257</v>
       </c>
@@ -23649,25 +23649,23 @@
       </c>
       <c r="J261" s="14" t="inlineStr">
         <is>
-          <t>1. Login di web, lalu sidebar &gt; Mills Setting (/mill-settings) sebagai MGR-A. Catat nilai awal Nama Aplikasi.
-2. Ubah nilai itu, tekan Simpan.
-3. Muat ulang halaman (F5). Baca nilainya.
+          <t>1. Login di web, lalu sidebar &gt; Mills Setting (/mill-settings) sebagai MGR-A. Catat posisi awal saklar "Kirim data langsung ke server saat
+disimpan" (aktif / nonaktif).
+2. Ubah posisinya, tekan Simpan.
+3. Muat ulang halaman (F5). Baca posisinya.
 4. Login di mobile (buka aplikasi, isi username dan password, tekan Login), mendarat di /home sebagai OPR-A pada mill yang sama, lalu sinkronkan bila diminta.
-5. Periksa bahwa nilai baru itu sudah ada di perangkat (tersinkron), lalu baca baris merek
-pada layar Home mobile.
-6. Kembalikan nilainya ke semula lewat Login di web, lalu sidebar &gt; Mills Setting (/mill-settings).</t>
+5. Periksa bahwa posisi baru itu sudah ada di perangkat (tersinkron).
+6. Kembalikan posisinya ke semula lewat Login di web, lalu sidebar &gt; Mills Setting (/mill-settings).</t>
         </is>
       </c>
       <c r="K261" s="14" t="inlineStr">
         <is>
           <t>- Simpan berhasil dengan pesan konfirmasi.
-- Nilai baru bertahan sesudah muat ulang.
-- Nilai baru sampai ke perangkat sesudah sinkronisasi — itu yang diperiksa langkah 4–5:
+- Posisi baru bertahan sesudah muat ulang.
+- Posisi baru sampai ke perangkat sesudah sinkronisasi — itu yang diperiksa langkah 4–5:
 jalur simpan → kirim → simpan di perangkat bekerja utuh.
-- Baris merek pada Home mobile tetap nama produk, TIDAK berubah mengikuti Nama Aplikasi.
-Itu bukan kegagalan: nama produk pada header memang terpisah dari Nama Aplikasi per mill.
-- Terbuka, dan bukan bagian dari kasus ini: Nama Aplikasi dan Logo saat ini tersimpan dan
-tersinkron tetapi belum dibaca layar mana pun. Keduanya menunggu layar yang memakainya.</t>
+- Nilai yang tersimpan tapi tidak berpengaruh ke layar atau perilaku mana pun adalah separuh
+fitur — itu yang dijaga kasus ini.</t>
         </is>
       </c>
       <c r="L261" s="11" t="inlineStr">
@@ -23677,8 +23675,8 @@
       </c>
       <c r="M261" s="14" t="inlineStr">
         <is>
-          <t>Catatan jalan: pengaturan di layar ini dipakai aplikasi mobile, bukan layar web mana pun — Gambar Halaman Utama pada Home mobile, saklar kirim-langsung pada penyimpanan Operator, dan Icon Station pada daftar stasiun mobile. Nama Aplikasi dan Logo adalah pengecualian: keduanya belum dibaca satu layar pun. Baris merek pada Home mobile memakai nama produk yang tetap, dan itu keputusan yang disengaja — nama produk pada header terpisah dari Nama Aplikasi per mill. Jadi langkah 1–3 dijalankan di web, dan langkah 4–5 harus dijalankan di aplikasi mobile untuk memeriksa bahwa nilainya sampai ke perangkat, bukan bahwa ia tampil di Home.
-pengaturan Jumlah Cages sudah tidak ada lagi di layar ini (jumlah cages kini diturunkan dari data mesin stasiun). Kalau Anda mencarinya karena pernah membacanya di versi dokumen lama, ketiadaannya bukan bug.</t>
+          <t>Catatan jalan: setiap pengaturan di layar ini dipakai aplikasi mobile, bukan layar web mana pun — Gambar Halaman Utama pada Home mobile, saklar "Kirim data langsung ke server saat disimpan" pada penyimpanan Operator, dan Icon Station pada daftar stasiun mobile. Jadi langkah 1–3 dijalankan di web, dan langkah 4–5 harus dijalankan di aplikasi mobile. Yang dipakai kasus ini adalah saklar kirim-langsung. Saklar itu tidak ditampilkan di layar mobile mana pun — ia mengubah perilaku penyimpanan — jadi yang diperiksa pada langkah 5 adalah nilainya sampai ke perangkat, bukan sesuatu yang tertulis di layar.
+tiga pengaturan sudah tidak ada lagi di layar ini, dan ketiadaannya bukan bug. Jumlah Cages — jumlah cages kini diturunkan dari data mesin stasiun. Nama Aplikasi dan Logo — tidak ada satu layar pun yang membacanya: baris merek pada Home mobile memakai nama produk yang tetap, terpisah dari nama aplikasi per mill. Kalau Anda mencari ketiganya karena pernah membacanya di versi dokumen lama, ketiganya memang sudah dicabut.</t>
         </is>
       </c>
       <c r="N261" s="17" t="inlineStr">
@@ -23699,7 +23697,7 @@
       <c r="Q261" s="17" t="n"/>
       <c r="R261" s="17" t="inlineStr">
         <is>
-          <t>Bagian web: Nama Aplikasi diubah dari "Business Unit A — Mill Smart Log" menjadi "Business Unit A — Mill Smart Log QA126949" — pesan konfirmasi=true, nilainya bertahan sesudah muat ulang=true. Bagian mobile: nilai barunya sampai ke perangkat=true (isi basis data lokal: [{"app_name":"Business Unit A — Mill Smart Log QA126949"}]). Baris merek Home berbunyi "Mills Smart Log" dan TIDAK mengikuti Nama Aplikasi (ikut berubah=false, dan false memang yang diharapkan): nama produk pada header terpisah dari Nama Aplikasi per mill. Langkah 6 — nilai Nama Aplikasi dikembalikan ke "Business Unit A — Mill Smart Log": berhasil, diperiksa ulang sesudah muat ulang. Terbuka: Nama Aplikasi dan Logo tersimpan serta tersinkron tetapi belum dibaca layar mana pun.</t>
+          <t>Bagian web: saklar "Kirim data langsung ke server saat disimpan" diubah dari nonaktif menjadi aktif — pesan konfirmasi=true, nilainya bertahan sesudah muat ulang=true. Bagian mobile: nilai barunya sampai ke perangkat=true (isi basis data lokal: [{"immediate_sync_enabled":1}]). Saklar ini tidak ditampilkan di layar mobile mana pun — ia mengubah PERILAKU penyimpanan — jadi yang dibaca di sini basis data lokalnya, bukan tulisan di layar. Langkah 6 — saklar dikembalikan ke nonaktif: berhasil, diperiksa ulang sesudah muat ulang. Catatan: Nama Aplikasi dan Logo DICABUT dari layar ini 2026-10-12 karena tidak ada layar yang membacanya; kasus ini karena itu memakai saklar kirim-langsung.</t>
         </is>
       </c>
     </row>
